--- a/output/version3/test/15-5/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
+++ b/output/version3/test/15-5/MARL/IL/RL-RL with pt (+comm+it)/(RL+RL) test results.xlsx
@@ -471,37 +471,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>612</v>
+        <v>512</v>
       </c>
       <c r="C2" t="n">
-        <v>648</v>
+        <v>594</v>
       </c>
       <c r="D2" t="n">
-        <v>669</v>
+        <v>602</v>
       </c>
       <c r="E2" t="n">
-        <v>620</v>
+        <v>611</v>
       </c>
       <c r="F2" t="n">
-        <v>600</v>
+        <v>626</v>
       </c>
       <c r="G2" t="n">
-        <v>578</v>
+        <v>591</v>
       </c>
       <c r="H2" t="n">
-        <v>647</v>
+        <v>580</v>
       </c>
       <c r="I2" t="n">
-        <v>634</v>
+        <v>565</v>
       </c>
       <c r="J2" t="n">
-        <v>566</v>
+        <v>541</v>
       </c>
       <c r="K2" t="n">
-        <v>629</v>
+        <v>592</v>
       </c>
       <c r="L2" t="n">
-        <v>620.3</v>
+        <v>581.4</v>
       </c>
     </row>
     <row r="3">
@@ -509,37 +509,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>672</v>
+        <v>755</v>
       </c>
       <c r="C3" t="n">
-        <v>700</v>
+        <v>731</v>
       </c>
       <c r="D3" t="n">
-        <v>680</v>
+        <v>646</v>
       </c>
       <c r="E3" t="n">
-        <v>768</v>
+        <v>714</v>
       </c>
       <c r="F3" t="n">
-        <v>719</v>
+        <v>626</v>
       </c>
       <c r="G3" t="n">
-        <v>748</v>
+        <v>818</v>
       </c>
       <c r="H3" t="n">
-        <v>762</v>
+        <v>687</v>
       </c>
       <c r="I3" t="n">
-        <v>696</v>
+        <v>701</v>
       </c>
       <c r="J3" t="n">
-        <v>666</v>
+        <v>692</v>
       </c>
       <c r="K3" t="n">
-        <v>775</v>
+        <v>724</v>
       </c>
       <c r="L3" t="n">
-        <v>718.6</v>
+        <v>709.4</v>
       </c>
     </row>
     <row r="4">
@@ -547,37 +547,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>690</v>
+        <v>666</v>
       </c>
       <c r="C4" t="n">
-        <v>684</v>
+        <v>769</v>
       </c>
       <c r="D4" t="n">
-        <v>865</v>
+        <v>735</v>
       </c>
       <c r="E4" t="n">
-        <v>718</v>
+        <v>715</v>
       </c>
       <c r="F4" t="n">
-        <v>643</v>
+        <v>722</v>
       </c>
       <c r="G4" t="n">
-        <v>665</v>
+        <v>754</v>
       </c>
       <c r="H4" t="n">
-        <v>636</v>
+        <v>641</v>
       </c>
       <c r="I4" t="n">
-        <v>702</v>
+        <v>673</v>
       </c>
       <c r="J4" t="n">
-        <v>666</v>
+        <v>670</v>
       </c>
       <c r="K4" t="n">
-        <v>719</v>
+        <v>757</v>
       </c>
       <c r="L4" t="n">
-        <v>698.8</v>
+        <v>710.2</v>
       </c>
     </row>
     <row r="5">
@@ -585,37 +585,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>780</v>
+        <v>859</v>
       </c>
       <c r="C5" t="n">
-        <v>870</v>
+        <v>724</v>
       </c>
       <c r="D5" t="n">
-        <v>778</v>
+        <v>888</v>
       </c>
       <c r="E5" t="n">
-        <v>822</v>
+        <v>816</v>
       </c>
       <c r="F5" t="n">
-        <v>824</v>
+        <v>811</v>
       </c>
       <c r="G5" t="n">
-        <v>854</v>
+        <v>801</v>
       </c>
       <c r="H5" t="n">
-        <v>846</v>
+        <v>823</v>
       </c>
       <c r="I5" t="n">
-        <v>837</v>
+        <v>831</v>
       </c>
       <c r="J5" t="n">
-        <v>808</v>
+        <v>861</v>
       </c>
       <c r="K5" t="n">
-        <v>862</v>
+        <v>841</v>
       </c>
       <c r="L5" t="n">
-        <v>828.1</v>
+        <v>825.5</v>
       </c>
     </row>
     <row r="6">
@@ -623,37 +623,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
+        <v>561</v>
+      </c>
+      <c r="C6" t="n">
         <v>655</v>
       </c>
-      <c r="C6" t="n">
-        <v>615</v>
-      </c>
       <c r="D6" t="n">
-        <v>550</v>
+        <v>655</v>
       </c>
       <c r="E6" t="n">
-        <v>579</v>
+        <v>603</v>
       </c>
       <c r="F6" t="n">
-        <v>709</v>
+        <v>624</v>
       </c>
       <c r="G6" t="n">
-        <v>642</v>
+        <v>616</v>
       </c>
       <c r="H6" t="n">
-        <v>677</v>
+        <v>669</v>
       </c>
       <c r="I6" t="n">
-        <v>576</v>
+        <v>684</v>
       </c>
       <c r="J6" t="n">
-        <v>546</v>
+        <v>669</v>
       </c>
       <c r="K6" t="n">
-        <v>637</v>
+        <v>595</v>
       </c>
       <c r="L6" t="n">
-        <v>618.6</v>
+        <v>633.1</v>
       </c>
     </row>
     <row r="7">
@@ -661,37 +661,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>844</v>
+        <v>881</v>
       </c>
       <c r="C7" t="n">
-        <v>869</v>
+        <v>793</v>
       </c>
       <c r="D7" t="n">
-        <v>831</v>
+        <v>716</v>
       </c>
       <c r="E7" t="n">
-        <v>766</v>
+        <v>688</v>
       </c>
       <c r="F7" t="n">
-        <v>883</v>
+        <v>843</v>
       </c>
       <c r="G7" t="n">
-        <v>768</v>
+        <v>783</v>
       </c>
       <c r="H7" t="n">
-        <v>779</v>
+        <v>749</v>
       </c>
       <c r="I7" t="n">
-        <v>796</v>
+        <v>853</v>
       </c>
       <c r="J7" t="n">
-        <v>832</v>
+        <v>759</v>
       </c>
       <c r="K7" t="n">
-        <v>821</v>
+        <v>761</v>
       </c>
       <c r="L7" t="n">
-        <v>818.9</v>
+        <v>782.6</v>
       </c>
     </row>
     <row r="8">
@@ -699,37 +699,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>696</v>
+        <v>643</v>
       </c>
       <c r="C8" t="n">
-        <v>622</v>
+        <v>705</v>
       </c>
       <c r="D8" t="n">
-        <v>695</v>
+        <v>667</v>
       </c>
       <c r="E8" t="n">
-        <v>733</v>
+        <v>689</v>
       </c>
       <c r="F8" t="n">
-        <v>666</v>
+        <v>662</v>
       </c>
       <c r="G8" t="n">
-        <v>680</v>
+        <v>637</v>
       </c>
       <c r="H8" t="n">
-        <v>670</v>
+        <v>693</v>
       </c>
       <c r="I8" t="n">
-        <v>695</v>
+        <v>735</v>
       </c>
       <c r="J8" t="n">
-        <v>645</v>
+        <v>701</v>
       </c>
       <c r="K8" t="n">
-        <v>705</v>
+        <v>612</v>
       </c>
       <c r="L8" t="n">
-        <v>680.7</v>
+        <v>674.4</v>
       </c>
     </row>
     <row r="9">
@@ -737,37 +737,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>680</v>
+        <v>692</v>
       </c>
       <c r="C9" t="n">
-        <v>658</v>
+        <v>624</v>
       </c>
       <c r="D9" t="n">
-        <v>642</v>
+        <v>597</v>
       </c>
       <c r="E9" t="n">
-        <v>581</v>
+        <v>607</v>
       </c>
       <c r="F9" t="n">
-        <v>731</v>
+        <v>626</v>
       </c>
       <c r="G9" t="n">
-        <v>678</v>
+        <v>627</v>
       </c>
       <c r="H9" t="n">
-        <v>618</v>
+        <v>670</v>
       </c>
       <c r="I9" t="n">
-        <v>573</v>
+        <v>709</v>
       </c>
       <c r="J9" t="n">
-        <v>701</v>
+        <v>763</v>
       </c>
       <c r="K9" t="n">
-        <v>641</v>
+        <v>650</v>
       </c>
       <c r="L9" t="n">
-        <v>650.3</v>
+        <v>656.5</v>
       </c>
     </row>
     <row r="10">
@@ -775,37 +775,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>674</v>
+        <v>692</v>
       </c>
       <c r="C10" t="n">
-        <v>705</v>
+        <v>753</v>
       </c>
       <c r="D10" t="n">
-        <v>757</v>
+        <v>738</v>
       </c>
       <c r="E10" t="n">
-        <v>653</v>
+        <v>688</v>
       </c>
       <c r="F10" t="n">
-        <v>777</v>
+        <v>707</v>
       </c>
       <c r="G10" t="n">
-        <v>746</v>
+        <v>780</v>
       </c>
       <c r="H10" t="n">
-        <v>752</v>
+        <v>804</v>
       </c>
       <c r="I10" t="n">
-        <v>721</v>
+        <v>662</v>
       </c>
       <c r="J10" t="n">
-        <v>709</v>
+        <v>675</v>
       </c>
       <c r="K10" t="n">
-        <v>803</v>
+        <v>809</v>
       </c>
       <c r="L10" t="n">
-        <v>729.7</v>
+        <v>730.8</v>
       </c>
     </row>
     <row r="11">
@@ -813,37 +813,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>706</v>
+        <v>762</v>
       </c>
       <c r="C11" t="n">
-        <v>733</v>
+        <v>712</v>
       </c>
       <c r="D11" t="n">
-        <v>761</v>
+        <v>815</v>
       </c>
       <c r="E11" t="n">
-        <v>648</v>
+        <v>815</v>
       </c>
       <c r="F11" t="n">
-        <v>755</v>
+        <v>702</v>
       </c>
       <c r="G11" t="n">
-        <v>706</v>
+        <v>794</v>
       </c>
       <c r="H11" t="n">
-        <v>795</v>
+        <v>724</v>
       </c>
       <c r="I11" t="n">
-        <v>826</v>
+        <v>718</v>
       </c>
       <c r="J11" t="n">
-        <v>773</v>
+        <v>737</v>
       </c>
       <c r="K11" t="n">
-        <v>758</v>
+        <v>689</v>
       </c>
       <c r="L11" t="n">
-        <v>746.1</v>
+        <v>746.8</v>
       </c>
     </row>
     <row r="12">
@@ -851,37 +851,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
+        <v>584</v>
+      </c>
+      <c r="C12" t="n">
+        <v>655</v>
+      </c>
+      <c r="D12" t="n">
+        <v>616</v>
+      </c>
+      <c r="E12" t="n">
+        <v>674</v>
+      </c>
+      <c r="F12" t="n">
         <v>663</v>
       </c>
-      <c r="C12" t="n">
-        <v>653</v>
-      </c>
-      <c r="D12" t="n">
-        <v>675</v>
-      </c>
-      <c r="E12" t="n">
-        <v>625</v>
-      </c>
-      <c r="F12" t="n">
-        <v>648</v>
-      </c>
       <c r="G12" t="n">
-        <v>670</v>
+        <v>683</v>
       </c>
       <c r="H12" t="n">
-        <v>654</v>
+        <v>644</v>
       </c>
       <c r="I12" t="n">
-        <v>604</v>
+        <v>679</v>
       </c>
       <c r="J12" t="n">
-        <v>640</v>
+        <v>685</v>
       </c>
       <c r="K12" t="n">
-        <v>630</v>
+        <v>684</v>
       </c>
       <c r="L12" t="n">
-        <v>646.2</v>
+        <v>656.7</v>
       </c>
     </row>
     <row r="13">
@@ -889,37 +889,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>540</v>
+        <v>569</v>
       </c>
       <c r="C13" t="n">
-        <v>573</v>
+        <v>596</v>
       </c>
       <c r="D13" t="n">
-        <v>572</v>
+        <v>594</v>
       </c>
       <c r="E13" t="n">
-        <v>613</v>
+        <v>542</v>
       </c>
       <c r="F13" t="n">
-        <v>572</v>
+        <v>564</v>
       </c>
       <c r="G13" t="n">
-        <v>531</v>
+        <v>591</v>
       </c>
       <c r="H13" t="n">
-        <v>705</v>
+        <v>538</v>
       </c>
       <c r="I13" t="n">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="J13" t="n">
-        <v>580</v>
+        <v>623</v>
       </c>
       <c r="K13" t="n">
-        <v>563</v>
+        <v>634</v>
       </c>
       <c r="L13" t="n">
-        <v>584.4</v>
+        <v>584.7</v>
       </c>
     </row>
     <row r="14">
@@ -927,37 +927,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>644</v>
+        <v>631</v>
       </c>
       <c r="C14" t="n">
+        <v>659</v>
+      </c>
+      <c r="D14" t="n">
+        <v>587</v>
+      </c>
+      <c r="E14" t="n">
+        <v>567</v>
+      </c>
+      <c r="F14" t="n">
+        <v>693</v>
+      </c>
+      <c r="G14" t="n">
+        <v>628</v>
+      </c>
+      <c r="H14" t="n">
         <v>589</v>
       </c>
-      <c r="D14" t="n">
-        <v>611</v>
-      </c>
-      <c r="E14" t="n">
-        <v>615</v>
-      </c>
-      <c r="F14" t="n">
-        <v>707</v>
-      </c>
-      <c r="G14" t="n">
-        <v>645</v>
-      </c>
-      <c r="H14" t="n">
-        <v>624</v>
-      </c>
       <c r="I14" t="n">
-        <v>680</v>
+        <v>659</v>
       </c>
       <c r="J14" t="n">
-        <v>708</v>
+        <v>642</v>
       </c>
       <c r="K14" t="n">
-        <v>676</v>
+        <v>636</v>
       </c>
       <c r="L14" t="n">
-        <v>649.9</v>
+        <v>629.1</v>
       </c>
     </row>
     <row r="15">
@@ -965,37 +965,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>778</v>
+        <v>708</v>
       </c>
       <c r="C15" t="n">
-        <v>691</v>
+        <v>698</v>
       </c>
       <c r="D15" t="n">
-        <v>680</v>
+        <v>715</v>
       </c>
       <c r="E15" t="n">
-        <v>645</v>
+        <v>724</v>
       </c>
       <c r="F15" t="n">
-        <v>698</v>
+        <v>725</v>
       </c>
       <c r="G15" t="n">
-        <v>735</v>
+        <v>620</v>
       </c>
       <c r="H15" t="n">
-        <v>693</v>
+        <v>642</v>
       </c>
       <c r="I15" t="n">
-        <v>683</v>
+        <v>681</v>
       </c>
       <c r="J15" t="n">
-        <v>706</v>
+        <v>635</v>
       </c>
       <c r="K15" t="n">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="L15" t="n">
-        <v>700</v>
+        <v>683.8</v>
       </c>
     </row>
     <row r="16">
@@ -1003,37 +1003,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>708</v>
+        <v>666</v>
       </c>
       <c r="C16" t="n">
-        <v>622</v>
+        <v>805</v>
       </c>
       <c r="D16" t="n">
-        <v>692</v>
+        <v>656</v>
       </c>
       <c r="E16" t="n">
-        <v>710</v>
+        <v>718</v>
       </c>
       <c r="F16" t="n">
-        <v>701</v>
+        <v>629</v>
       </c>
       <c r="G16" t="n">
-        <v>696</v>
+        <v>668</v>
       </c>
       <c r="H16" t="n">
-        <v>779</v>
+        <v>656</v>
       </c>
       <c r="I16" t="n">
-        <v>736</v>
+        <v>704</v>
       </c>
       <c r="J16" t="n">
-        <v>693</v>
+        <v>658</v>
       </c>
       <c r="K16" t="n">
-        <v>731</v>
+        <v>677</v>
       </c>
       <c r="L16" t="n">
-        <v>706.8</v>
+        <v>683.7</v>
       </c>
     </row>
     <row r="17">
@@ -1041,37 +1041,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>769</v>
+        <v>762</v>
       </c>
       <c r="C17" t="n">
-        <v>685</v>
+        <v>782</v>
       </c>
       <c r="D17" t="n">
-        <v>773</v>
+        <v>728</v>
       </c>
       <c r="E17" t="n">
-        <v>803</v>
+        <v>689</v>
       </c>
       <c r="F17" t="n">
-        <v>782</v>
+        <v>823</v>
       </c>
       <c r="G17" t="n">
-        <v>743</v>
+        <v>781</v>
       </c>
       <c r="H17" t="n">
-        <v>728</v>
+        <v>807</v>
       </c>
       <c r="I17" t="n">
-        <v>828</v>
+        <v>732</v>
       </c>
       <c r="J17" t="n">
-        <v>731</v>
+        <v>763</v>
       </c>
       <c r="K17" t="n">
-        <v>786</v>
+        <v>768</v>
       </c>
       <c r="L17" t="n">
-        <v>762.8</v>
+        <v>763.5</v>
       </c>
     </row>
     <row r="18">
@@ -1079,37 +1079,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>577</v>
+        <v>619</v>
       </c>
       <c r="C18" t="n">
-        <v>643</v>
+        <v>578</v>
       </c>
       <c r="D18" t="n">
-        <v>655</v>
+        <v>611</v>
       </c>
       <c r="E18" t="n">
-        <v>706</v>
+        <v>621</v>
       </c>
       <c r="F18" t="n">
-        <v>660</v>
+        <v>657</v>
       </c>
       <c r="G18" t="n">
-        <v>581</v>
+        <v>636</v>
       </c>
       <c r="H18" t="n">
-        <v>629</v>
+        <v>638</v>
       </c>
       <c r="I18" t="n">
-        <v>658</v>
+        <v>690</v>
       </c>
       <c r="J18" t="n">
-        <v>664</v>
+        <v>650</v>
       </c>
       <c r="K18" t="n">
-        <v>675</v>
+        <v>656</v>
       </c>
       <c r="L18" t="n">
-        <v>644.8</v>
+        <v>635.6</v>
       </c>
     </row>
     <row r="19">
@@ -1117,37 +1117,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>669</v>
+        <v>695</v>
       </c>
       <c r="C19" t="n">
-        <v>660</v>
+        <v>744</v>
       </c>
       <c r="D19" t="n">
-        <v>732</v>
+        <v>649</v>
       </c>
       <c r="E19" t="n">
-        <v>691</v>
+        <v>684</v>
       </c>
       <c r="F19" t="n">
-        <v>656</v>
+        <v>717</v>
       </c>
       <c r="G19" t="n">
-        <v>636</v>
+        <v>652</v>
       </c>
       <c r="H19" t="n">
-        <v>643</v>
+        <v>701</v>
       </c>
       <c r="I19" t="n">
-        <v>649</v>
+        <v>676</v>
       </c>
       <c r="J19" t="n">
-        <v>678</v>
+        <v>661</v>
       </c>
       <c r="K19" t="n">
-        <v>668</v>
+        <v>718</v>
       </c>
       <c r="L19" t="n">
-        <v>668.2</v>
+        <v>689.7</v>
       </c>
     </row>
     <row r="20">
@@ -1155,37 +1155,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>695</v>
+        <v>717</v>
       </c>
       <c r="C20" t="n">
-        <v>688</v>
+        <v>631</v>
       </c>
       <c r="D20" t="n">
-        <v>577</v>
+        <v>623</v>
       </c>
       <c r="E20" t="n">
-        <v>638</v>
+        <v>678</v>
       </c>
       <c r="F20" t="n">
-        <v>674</v>
+        <v>555</v>
       </c>
       <c r="G20" t="n">
-        <v>634</v>
+        <v>609</v>
       </c>
       <c r="H20" t="n">
-        <v>637</v>
+        <v>676</v>
       </c>
       <c r="I20" t="n">
-        <v>702</v>
+        <v>594</v>
       </c>
       <c r="J20" t="n">
-        <v>625</v>
+        <v>630</v>
       </c>
       <c r="K20" t="n">
-        <v>719</v>
+        <v>658</v>
       </c>
       <c r="L20" t="n">
-        <v>658.9</v>
+        <v>637.1</v>
       </c>
     </row>
     <row r="21">
@@ -1193,37 +1193,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
+        <v>627</v>
+      </c>
+      <c r="C21" t="n">
+        <v>585</v>
+      </c>
+      <c r="D21" t="n">
+        <v>655</v>
+      </c>
+      <c r="E21" t="n">
+        <v>737</v>
+      </c>
+      <c r="F21" t="n">
+        <v>624</v>
+      </c>
+      <c r="G21" t="n">
+        <v>692</v>
+      </c>
+      <c r="H21" t="n">
+        <v>673</v>
+      </c>
+      <c r="I21" t="n">
+        <v>671</v>
+      </c>
+      <c r="J21" t="n">
         <v>630</v>
       </c>
-      <c r="C21" t="n">
-        <v>568</v>
-      </c>
-      <c r="D21" t="n">
-        <v>572</v>
-      </c>
-      <c r="E21" t="n">
-        <v>670</v>
-      </c>
-      <c r="F21" t="n">
-        <v>587</v>
-      </c>
-      <c r="G21" t="n">
-        <v>669</v>
-      </c>
-      <c r="H21" t="n">
-        <v>620</v>
-      </c>
-      <c r="I21" t="n">
-        <v>590</v>
-      </c>
-      <c r="J21" t="n">
-        <v>563</v>
-      </c>
       <c r="K21" t="n">
-        <v>636</v>
+        <v>653</v>
       </c>
       <c r="L21" t="n">
-        <v>610.5</v>
+        <v>654.7</v>
       </c>
     </row>
     <row r="22">
@@ -1231,37 +1231,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>581</v>
+        <v>684</v>
       </c>
       <c r="C22" t="n">
-        <v>560</v>
+        <v>614</v>
       </c>
       <c r="D22" t="n">
-        <v>545</v>
+        <v>566</v>
       </c>
       <c r="E22" t="n">
-        <v>567</v>
+        <v>551</v>
       </c>
       <c r="F22" t="n">
-        <v>648</v>
+        <v>641</v>
       </c>
       <c r="G22" t="n">
-        <v>566</v>
+        <v>599</v>
       </c>
       <c r="H22" t="n">
+        <v>618</v>
+      </c>
+      <c r="I22" t="n">
+        <v>651</v>
+      </c>
+      <c r="J22" t="n">
         <v>608</v>
       </c>
-      <c r="I22" t="n">
-        <v>625</v>
-      </c>
-      <c r="J22" t="n">
-        <v>583</v>
-      </c>
       <c r="K22" t="n">
-        <v>574</v>
+        <v>678</v>
       </c>
       <c r="L22" t="n">
-        <v>585.7</v>
+        <v>621</v>
       </c>
     </row>
     <row r="23">
@@ -1269,37 +1269,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>670</v>
+        <v>708</v>
       </c>
       <c r="C23" t="n">
-        <v>759</v>
+        <v>709</v>
       </c>
       <c r="D23" t="n">
-        <v>639</v>
+        <v>676</v>
       </c>
       <c r="E23" t="n">
-        <v>701</v>
+        <v>649</v>
       </c>
       <c r="F23" t="n">
-        <v>689</v>
+        <v>636</v>
       </c>
       <c r="G23" t="n">
-        <v>664</v>
+        <v>699</v>
       </c>
       <c r="H23" t="n">
-        <v>777</v>
+        <v>790</v>
       </c>
       <c r="I23" t="n">
-        <v>684</v>
+        <v>687</v>
       </c>
       <c r="J23" t="n">
-        <v>680</v>
+        <v>641</v>
       </c>
       <c r="K23" t="n">
-        <v>705</v>
+        <v>615</v>
       </c>
       <c r="L23" t="n">
-        <v>696.8</v>
+        <v>681</v>
       </c>
     </row>
     <row r="24">
@@ -1307,37 +1307,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>743</v>
+        <v>692</v>
       </c>
       <c r="C24" t="n">
-        <v>683</v>
+        <v>655</v>
       </c>
       <c r="D24" t="n">
-        <v>700</v>
+        <v>708</v>
       </c>
       <c r="E24" t="n">
-        <v>732</v>
+        <v>794</v>
       </c>
       <c r="F24" t="n">
-        <v>744</v>
+        <v>649</v>
       </c>
       <c r="G24" t="n">
-        <v>662</v>
+        <v>692</v>
       </c>
       <c r="H24" t="n">
-        <v>659</v>
+        <v>673</v>
       </c>
       <c r="I24" t="n">
-        <v>761</v>
+        <v>653</v>
       </c>
       <c r="J24" t="n">
-        <v>673</v>
+        <v>764</v>
       </c>
       <c r="K24" t="n">
-        <v>692</v>
+        <v>660</v>
       </c>
       <c r="L24" t="n">
-        <v>704.9</v>
+        <v>694</v>
       </c>
     </row>
     <row r="25">
@@ -1345,37 +1345,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>676</v>
+        <v>625</v>
       </c>
       <c r="C25" t="n">
-        <v>667</v>
+        <v>597</v>
       </c>
       <c r="D25" t="n">
-        <v>677</v>
+        <v>614</v>
       </c>
       <c r="E25" t="n">
-        <v>711</v>
+        <v>597</v>
       </c>
       <c r="F25" t="n">
-        <v>576</v>
+        <v>622</v>
       </c>
       <c r="G25" t="n">
-        <v>616</v>
+        <v>623</v>
       </c>
       <c r="H25" t="n">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="I25" t="n">
-        <v>650</v>
+        <v>681</v>
       </c>
       <c r="J25" t="n">
-        <v>605</v>
+        <v>684</v>
       </c>
       <c r="K25" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="L25" t="n">
-        <v>653</v>
+        <v>638.6</v>
       </c>
     </row>
     <row r="26">
@@ -1383,37 +1383,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>661</v>
+        <v>671</v>
       </c>
       <c r="C26" t="n">
-        <v>794</v>
+        <v>784</v>
       </c>
       <c r="D26" t="n">
-        <v>762</v>
+        <v>745</v>
       </c>
       <c r="E26" t="n">
-        <v>735</v>
+        <v>667</v>
       </c>
       <c r="F26" t="n">
-        <v>700</v>
+        <v>645</v>
       </c>
       <c r="G26" t="n">
-        <v>710</v>
+        <v>682</v>
       </c>
       <c r="H26" t="n">
-        <v>697</v>
+        <v>716</v>
       </c>
       <c r="I26" t="n">
-        <v>747</v>
+        <v>702</v>
       </c>
       <c r="J26" t="n">
-        <v>751</v>
+        <v>708</v>
       </c>
       <c r="K26" t="n">
-        <v>703</v>
+        <v>724</v>
       </c>
       <c r="L26" t="n">
-        <v>726</v>
+        <v>704.4</v>
       </c>
     </row>
     <row r="27">
@@ -1421,37 +1421,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>752</v>
+        <v>739</v>
       </c>
       <c r="C27" t="n">
-        <v>768</v>
+        <v>697</v>
       </c>
       <c r="D27" t="n">
-        <v>805</v>
+        <v>765</v>
       </c>
       <c r="E27" t="n">
-        <v>749</v>
+        <v>724</v>
       </c>
       <c r="F27" t="n">
-        <v>765</v>
+        <v>694</v>
       </c>
       <c r="G27" t="n">
-        <v>705</v>
+        <v>666</v>
       </c>
       <c r="H27" t="n">
-        <v>707</v>
+        <v>682</v>
       </c>
       <c r="I27" t="n">
-        <v>734</v>
+        <v>748</v>
       </c>
       <c r="J27" t="n">
-        <v>751</v>
+        <v>682</v>
       </c>
       <c r="K27" t="n">
-        <v>666</v>
+        <v>700</v>
       </c>
       <c r="L27" t="n">
-        <v>740.2</v>
+        <v>709.7</v>
       </c>
     </row>
     <row r="28">
@@ -1459,37 +1459,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>618</v>
+        <v>596</v>
       </c>
       <c r="C28" t="n">
-        <v>747</v>
+        <v>571</v>
       </c>
       <c r="D28" t="n">
-        <v>586</v>
+        <v>624</v>
       </c>
       <c r="E28" t="n">
-        <v>623</v>
+        <v>657</v>
       </c>
       <c r="F28" t="n">
-        <v>640</v>
+        <v>626</v>
       </c>
       <c r="G28" t="n">
-        <v>568</v>
+        <v>617</v>
       </c>
       <c r="H28" t="n">
-        <v>635</v>
+        <v>579</v>
       </c>
       <c r="I28" t="n">
-        <v>636</v>
+        <v>588</v>
       </c>
       <c r="J28" t="n">
-        <v>704</v>
+        <v>662</v>
       </c>
       <c r="K28" t="n">
-        <v>650</v>
+        <v>617</v>
       </c>
       <c r="L28" t="n">
-        <v>640.7</v>
+        <v>613.7</v>
       </c>
     </row>
     <row r="29">
@@ -1497,37 +1497,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>724</v>
+        <v>663</v>
       </c>
       <c r="C29" t="n">
-        <v>638</v>
+        <v>654</v>
       </c>
       <c r="D29" t="n">
-        <v>723</v>
+        <v>734</v>
       </c>
       <c r="E29" t="n">
-        <v>609</v>
+        <v>649</v>
       </c>
       <c r="F29" t="n">
-        <v>733</v>
+        <v>656</v>
       </c>
       <c r="G29" t="n">
-        <v>613</v>
+        <v>647</v>
       </c>
       <c r="H29" t="n">
-        <v>696</v>
+        <v>702</v>
       </c>
       <c r="I29" t="n">
-        <v>618</v>
+        <v>719</v>
       </c>
       <c r="J29" t="n">
-        <v>664</v>
+        <v>688</v>
       </c>
       <c r="K29" t="n">
-        <v>632</v>
+        <v>661</v>
       </c>
       <c r="L29" t="n">
-        <v>665</v>
+        <v>677.3</v>
       </c>
     </row>
     <row r="30">
@@ -1535,37 +1535,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>692</v>
+        <v>731</v>
       </c>
       <c r="C30" t="n">
-        <v>642</v>
+        <v>696</v>
       </c>
       <c r="D30" t="n">
-        <v>709</v>
+        <v>648</v>
       </c>
       <c r="E30" t="n">
-        <v>677</v>
+        <v>673</v>
       </c>
       <c r="F30" t="n">
+        <v>713</v>
+      </c>
+      <c r="G30" t="n">
+        <v>668</v>
+      </c>
+      <c r="H30" t="n">
+        <v>658</v>
+      </c>
+      <c r="I30" t="n">
+        <v>743</v>
+      </c>
+      <c r="J30" t="n">
         <v>726</v>
       </c>
-      <c r="G30" t="n">
-        <v>783</v>
-      </c>
-      <c r="H30" t="n">
-        <v>793</v>
-      </c>
-      <c r="I30" t="n">
-        <v>751</v>
-      </c>
-      <c r="J30" t="n">
-        <v>767</v>
-      </c>
       <c r="K30" t="n">
-        <v>654</v>
+        <v>645</v>
       </c>
       <c r="L30" t="n">
-        <v>719.4</v>
+        <v>690.1</v>
       </c>
     </row>
     <row r="31">
@@ -1573,37 +1573,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>646</v>
+        <v>632</v>
       </c>
       <c r="C31" t="n">
-        <v>681</v>
+        <v>647</v>
       </c>
       <c r="D31" t="n">
-        <v>650</v>
+        <v>727</v>
       </c>
       <c r="E31" t="n">
-        <v>669</v>
+        <v>608</v>
       </c>
       <c r="F31" t="n">
-        <v>645</v>
+        <v>643</v>
       </c>
       <c r="G31" t="n">
-        <v>689</v>
+        <v>653</v>
       </c>
       <c r="H31" t="n">
-        <v>690</v>
+        <v>679</v>
       </c>
       <c r="I31" t="n">
-        <v>703</v>
+        <v>647</v>
       </c>
       <c r="J31" t="n">
-        <v>663</v>
+        <v>640</v>
       </c>
       <c r="K31" t="n">
-        <v>634</v>
+        <v>685</v>
       </c>
       <c r="L31" t="n">
-        <v>667</v>
+        <v>656.1</v>
       </c>
     </row>
     <row r="32">
@@ -1611,37 +1611,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>682</v>
+        <v>617</v>
       </c>
       <c r="C32" t="n">
-        <v>562</v>
+        <v>631</v>
       </c>
       <c r="D32" t="n">
-        <v>661</v>
+        <v>616</v>
       </c>
       <c r="E32" t="n">
-        <v>647</v>
+        <v>652</v>
       </c>
       <c r="F32" t="n">
-        <v>724</v>
+        <v>722</v>
       </c>
       <c r="G32" t="n">
-        <v>620</v>
+        <v>648</v>
       </c>
       <c r="H32" t="n">
-        <v>576</v>
+        <v>607</v>
       </c>
       <c r="I32" t="n">
-        <v>669</v>
+        <v>588</v>
       </c>
       <c r="J32" t="n">
-        <v>589</v>
+        <v>605</v>
       </c>
       <c r="K32" t="n">
-        <v>612</v>
+        <v>763</v>
       </c>
       <c r="L32" t="n">
-        <v>634.2</v>
+        <v>644.9</v>
       </c>
     </row>
     <row r="33">
@@ -1649,37 +1649,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>767</v>
+        <v>734</v>
       </c>
       <c r="C33" t="n">
-        <v>770</v>
+        <v>803</v>
       </c>
       <c r="D33" t="n">
-        <v>718</v>
+        <v>841</v>
       </c>
       <c r="E33" t="n">
-        <v>792</v>
+        <v>698</v>
       </c>
       <c r="F33" t="n">
-        <v>800</v>
+        <v>696</v>
       </c>
       <c r="G33" t="n">
-        <v>814</v>
+        <v>746</v>
       </c>
       <c r="H33" t="n">
-        <v>694</v>
+        <v>746</v>
       </c>
       <c r="I33" t="n">
-        <v>703</v>
+        <v>816</v>
       </c>
       <c r="J33" t="n">
-        <v>703</v>
+        <v>670</v>
       </c>
       <c r="K33" t="n">
-        <v>775</v>
+        <v>738</v>
       </c>
       <c r="L33" t="n">
-        <v>753.6</v>
+        <v>748.8</v>
       </c>
     </row>
     <row r="34">
@@ -1687,37 +1687,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>633</v>
+        <v>682</v>
       </c>
       <c r="C34" t="n">
-        <v>592</v>
+        <v>614</v>
       </c>
       <c r="D34" t="n">
-        <v>626</v>
+        <v>683</v>
       </c>
       <c r="E34" t="n">
-        <v>582</v>
+        <v>738</v>
       </c>
       <c r="F34" t="n">
-        <v>615</v>
+        <v>645</v>
       </c>
       <c r="G34" t="n">
-        <v>667</v>
+        <v>685</v>
       </c>
       <c r="H34" t="n">
-        <v>619</v>
+        <v>559</v>
       </c>
       <c r="I34" t="n">
-        <v>683</v>
+        <v>600</v>
       </c>
       <c r="J34" t="n">
-        <v>583</v>
+        <v>549</v>
       </c>
       <c r="K34" t="n">
-        <v>619</v>
+        <v>644</v>
       </c>
       <c r="L34" t="n">
-        <v>621.9</v>
+        <v>639.9</v>
       </c>
     </row>
     <row r="35">
@@ -1725,37 +1725,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>657</v>
+        <v>776</v>
       </c>
       <c r="C35" t="n">
-        <v>671</v>
+        <v>764</v>
       </c>
       <c r="D35" t="n">
+        <v>849</v>
+      </c>
+      <c r="E35" t="n">
         <v>786</v>
       </c>
-      <c r="E35" t="n">
-        <v>717</v>
-      </c>
       <c r="F35" t="n">
-        <v>874</v>
+        <v>686</v>
       </c>
       <c r="G35" t="n">
-        <v>753</v>
+        <v>708</v>
       </c>
       <c r="H35" t="n">
-        <v>665</v>
+        <v>792</v>
       </c>
       <c r="I35" t="n">
-        <v>760</v>
+        <v>758</v>
       </c>
       <c r="J35" t="n">
-        <v>794</v>
+        <v>768</v>
       </c>
       <c r="K35" t="n">
-        <v>689</v>
+        <v>772</v>
       </c>
       <c r="L35" t="n">
-        <v>736.6</v>
+        <v>765.9</v>
       </c>
     </row>
     <row r="36">
@@ -1763,37 +1763,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
+        <v>577</v>
+      </c>
+      <c r="C36" t="n">
+        <v>589</v>
+      </c>
+      <c r="D36" t="n">
+        <v>597</v>
+      </c>
+      <c r="E36" t="n">
+        <v>629</v>
+      </c>
+      <c r="F36" t="n">
+        <v>557</v>
+      </c>
+      <c r="G36" t="n">
+        <v>586</v>
+      </c>
+      <c r="H36" t="n">
+        <v>600</v>
+      </c>
+      <c r="I36" t="n">
+        <v>630</v>
+      </c>
+      <c r="J36" t="n">
+        <v>578</v>
+      </c>
+      <c r="K36" t="n">
         <v>604</v>
       </c>
-      <c r="C36" t="n">
-        <v>578</v>
-      </c>
-      <c r="D36" t="n">
-        <v>579</v>
-      </c>
-      <c r="E36" t="n">
-        <v>615</v>
-      </c>
-      <c r="F36" t="n">
-        <v>673</v>
-      </c>
-      <c r="G36" t="n">
-        <v>589</v>
-      </c>
-      <c r="H36" t="n">
-        <v>594</v>
-      </c>
-      <c r="I36" t="n">
-        <v>557</v>
-      </c>
-      <c r="J36" t="n">
-        <v>581</v>
-      </c>
-      <c r="K36" t="n">
-        <v>574</v>
-      </c>
       <c r="L36" t="n">
-        <v>594.4</v>
+        <v>594.7</v>
       </c>
     </row>
     <row r="37">
@@ -1801,37 +1801,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>609</v>
+        <v>648</v>
       </c>
       <c r="C37" t="n">
-        <v>735</v>
+        <v>687</v>
       </c>
       <c r="D37" t="n">
-        <v>659</v>
+        <v>679</v>
       </c>
       <c r="E37" t="n">
-        <v>718</v>
+        <v>700</v>
       </c>
       <c r="F37" t="n">
-        <v>626</v>
+        <v>697</v>
       </c>
       <c r="G37" t="n">
-        <v>673</v>
+        <v>685</v>
       </c>
       <c r="H37" t="n">
-        <v>703</v>
+        <v>710</v>
       </c>
       <c r="I37" t="n">
-        <v>691</v>
+        <v>717</v>
       </c>
       <c r="J37" t="n">
-        <v>666</v>
+        <v>758</v>
       </c>
       <c r="K37" t="n">
-        <v>611</v>
+        <v>721</v>
       </c>
       <c r="L37" t="n">
-        <v>669.1</v>
+        <v>700.2</v>
       </c>
     </row>
     <row r="38">
@@ -1839,37 +1839,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>701</v>
+        <v>717</v>
       </c>
       <c r="C38" t="n">
-        <v>704</v>
+        <v>708</v>
       </c>
       <c r="D38" t="n">
-        <v>721</v>
+        <v>654</v>
       </c>
       <c r="E38" t="n">
-        <v>637</v>
+        <v>753</v>
       </c>
       <c r="F38" t="n">
-        <v>639</v>
+        <v>684</v>
       </c>
       <c r="G38" t="n">
-        <v>648</v>
+        <v>708</v>
       </c>
       <c r="H38" t="n">
-        <v>710</v>
+        <v>690</v>
       </c>
       <c r="I38" t="n">
-        <v>692</v>
+        <v>640</v>
       </c>
       <c r="J38" t="n">
-        <v>711</v>
+        <v>638</v>
       </c>
       <c r="K38" t="n">
-        <v>742</v>
+        <v>758</v>
       </c>
       <c r="L38" t="n">
-        <v>690.5</v>
+        <v>695</v>
       </c>
     </row>
     <row r="39">
@@ -1877,37 +1877,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>481</v>
+        <v>581</v>
       </c>
       <c r="C39" t="n">
-        <v>571</v>
+        <v>606</v>
       </c>
       <c r="D39" t="n">
-        <v>625</v>
+        <v>597</v>
       </c>
       <c r="E39" t="n">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="F39" t="n">
-        <v>604</v>
+        <v>595</v>
       </c>
       <c r="G39" t="n">
-        <v>590</v>
+        <v>579</v>
       </c>
       <c r="H39" t="n">
-        <v>557</v>
+        <v>579</v>
       </c>
       <c r="I39" t="n">
-        <v>663</v>
+        <v>561</v>
       </c>
       <c r="J39" t="n">
-        <v>578</v>
+        <v>493</v>
       </c>
       <c r="K39" t="n">
-        <v>608</v>
+        <v>652</v>
       </c>
       <c r="L39" t="n">
-        <v>585.3</v>
+        <v>582</v>
       </c>
     </row>
     <row r="40">
@@ -1915,37 +1915,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>687</v>
+        <v>808</v>
       </c>
       <c r="C40" t="n">
-        <v>661</v>
+        <v>683</v>
       </c>
       <c r="D40" t="n">
-        <v>672</v>
+        <v>731</v>
       </c>
       <c r="E40" t="n">
-        <v>745</v>
+        <v>724</v>
       </c>
       <c r="F40" t="n">
-        <v>810</v>
+        <v>609</v>
       </c>
       <c r="G40" t="n">
-        <v>739</v>
+        <v>684</v>
       </c>
       <c r="H40" t="n">
-        <v>727</v>
+        <v>685</v>
       </c>
       <c r="I40" t="n">
-        <v>716</v>
+        <v>678</v>
       </c>
       <c r="J40" t="n">
-        <v>740</v>
+        <v>718</v>
       </c>
       <c r="K40" t="n">
-        <v>664</v>
+        <v>627</v>
       </c>
       <c r="L40" t="n">
-        <v>716.1</v>
+        <v>694.7</v>
       </c>
     </row>
     <row r="41">
@@ -1953,37 +1953,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>709</v>
+        <v>606</v>
       </c>
       <c r="C41" t="n">
-        <v>627</v>
+        <v>695</v>
       </c>
       <c r="D41" t="n">
-        <v>714</v>
+        <v>696</v>
       </c>
       <c r="E41" t="n">
-        <v>617</v>
+        <v>658</v>
       </c>
       <c r="F41" t="n">
-        <v>631</v>
+        <v>596</v>
       </c>
       <c r="G41" t="n">
-        <v>714</v>
+        <v>605</v>
       </c>
       <c r="H41" t="n">
-        <v>636</v>
+        <v>671</v>
       </c>
       <c r="I41" t="n">
-        <v>627</v>
+        <v>610</v>
       </c>
       <c r="J41" t="n">
-        <v>651</v>
+        <v>622</v>
       </c>
       <c r="K41" t="n">
-        <v>594</v>
+        <v>695</v>
       </c>
       <c r="L41" t="n">
-        <v>652</v>
+        <v>645.4</v>
       </c>
     </row>
     <row r="42">
@@ -1991,37 +1991,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>618</v>
+        <v>626</v>
       </c>
       <c r="C42" t="n">
-        <v>618</v>
+        <v>639</v>
       </c>
       <c r="D42" t="n">
-        <v>599</v>
+        <v>577</v>
       </c>
       <c r="E42" t="n">
-        <v>552</v>
+        <v>656</v>
       </c>
       <c r="F42" t="n">
-        <v>534</v>
+        <v>588</v>
       </c>
       <c r="G42" t="n">
-        <v>612</v>
+        <v>627</v>
       </c>
       <c r="H42" t="n">
+        <v>547</v>
+      </c>
+      <c r="I42" t="n">
+        <v>593</v>
+      </c>
+      <c r="J42" t="n">
+        <v>735</v>
+      </c>
+      <c r="K42" t="n">
         <v>567</v>
       </c>
-      <c r="I42" t="n">
-        <v>647</v>
-      </c>
-      <c r="J42" t="n">
-        <v>630</v>
-      </c>
-      <c r="K42" t="n">
-        <v>685</v>
-      </c>
       <c r="L42" t="n">
-        <v>606.2</v>
+        <v>615.5</v>
       </c>
     </row>
     <row r="43">
@@ -2029,37 +2029,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>752</v>
+        <v>720</v>
       </c>
       <c r="C43" t="n">
-        <v>768</v>
+        <v>699</v>
       </c>
       <c r="D43" t="n">
-        <v>650</v>
+        <v>597</v>
       </c>
       <c r="E43" t="n">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="F43" t="n">
-        <v>638</v>
+        <v>699</v>
       </c>
       <c r="G43" t="n">
-        <v>661</v>
+        <v>698</v>
       </c>
       <c r="H43" t="n">
-        <v>674</v>
+        <v>584</v>
       </c>
       <c r="I43" t="n">
-        <v>723</v>
+        <v>671</v>
       </c>
       <c r="J43" t="n">
-        <v>624</v>
+        <v>656</v>
       </c>
       <c r="K43" t="n">
-        <v>659</v>
+        <v>635</v>
       </c>
       <c r="L43" t="n">
-        <v>681.8</v>
+        <v>662.7</v>
       </c>
     </row>
     <row r="44">
@@ -2067,37 +2067,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>738</v>
+        <v>748</v>
       </c>
       <c r="C44" t="n">
-        <v>712</v>
+        <v>680</v>
       </c>
       <c r="D44" t="n">
-        <v>741</v>
+        <v>632</v>
       </c>
       <c r="E44" t="n">
-        <v>689</v>
+        <v>729</v>
       </c>
       <c r="F44" t="n">
-        <v>758</v>
+        <v>680</v>
       </c>
       <c r="G44" t="n">
-        <v>753</v>
+        <v>767</v>
       </c>
       <c r="H44" t="n">
-        <v>804</v>
+        <v>692</v>
       </c>
       <c r="I44" t="n">
-        <v>765</v>
+        <v>677</v>
       </c>
       <c r="J44" t="n">
-        <v>705</v>
+        <v>683</v>
       </c>
       <c r="K44" t="n">
-        <v>651</v>
+        <v>692</v>
       </c>
       <c r="L44" t="n">
-        <v>731.6</v>
+        <v>698</v>
       </c>
     </row>
     <row r="45">
@@ -2105,37 +2105,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>611</v>
+        <v>622</v>
       </c>
       <c r="C45" t="n">
-        <v>612</v>
+        <v>590</v>
       </c>
       <c r="D45" t="n">
-        <v>580</v>
+        <v>607</v>
       </c>
       <c r="E45" t="n">
-        <v>607</v>
+        <v>583</v>
       </c>
       <c r="F45" t="n">
-        <v>643</v>
+        <v>645</v>
       </c>
       <c r="G45" t="n">
-        <v>607</v>
+        <v>597</v>
       </c>
       <c r="H45" t="n">
-        <v>708</v>
+        <v>597</v>
       </c>
       <c r="I45" t="n">
-        <v>681</v>
+        <v>628</v>
       </c>
       <c r="J45" t="n">
-        <v>561</v>
+        <v>631</v>
       </c>
       <c r="K45" t="n">
-        <v>610</v>
+        <v>582</v>
       </c>
       <c r="L45" t="n">
-        <v>622</v>
+        <v>608.2</v>
       </c>
     </row>
     <row r="46">
@@ -2143,37 +2143,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>685</v>
+        <v>613</v>
       </c>
       <c r="C46" t="n">
-        <v>665</v>
+        <v>559</v>
       </c>
       <c r="D46" t="n">
-        <v>614</v>
+        <v>667</v>
       </c>
       <c r="E46" t="n">
-        <v>650</v>
+        <v>645</v>
       </c>
       <c r="F46" t="n">
-        <v>644</v>
+        <v>618</v>
       </c>
       <c r="G46" t="n">
-        <v>584</v>
+        <v>630</v>
       </c>
       <c r="H46" t="n">
-        <v>632</v>
+        <v>598</v>
       </c>
       <c r="I46" t="n">
-        <v>589</v>
+        <v>755</v>
       </c>
       <c r="J46" t="n">
-        <v>620</v>
+        <v>684</v>
       </c>
       <c r="K46" t="n">
-        <v>656</v>
+        <v>603</v>
       </c>
       <c r="L46" t="n">
-        <v>633.9</v>
+        <v>637.2</v>
       </c>
     </row>
     <row r="47">
@@ -2181,37 +2181,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>718</v>
+        <v>775</v>
       </c>
       <c r="C47" t="n">
-        <v>641</v>
+        <v>656</v>
       </c>
       <c r="D47" t="n">
-        <v>661</v>
+        <v>710</v>
       </c>
       <c r="E47" t="n">
+        <v>662</v>
+      </c>
+      <c r="F47" t="n">
         <v>664</v>
       </c>
-      <c r="F47" t="n">
-        <v>648</v>
-      </c>
       <c r="G47" t="n">
-        <v>738</v>
+        <v>731</v>
       </c>
       <c r="H47" t="n">
-        <v>804</v>
+        <v>693</v>
       </c>
       <c r="I47" t="n">
-        <v>700</v>
+        <v>719</v>
       </c>
       <c r="J47" t="n">
-        <v>794</v>
+        <v>820</v>
       </c>
       <c r="K47" t="n">
-        <v>665</v>
+        <v>767</v>
       </c>
       <c r="L47" t="n">
-        <v>703.3</v>
+        <v>719.7</v>
       </c>
     </row>
     <row r="48">
@@ -2219,37 +2219,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>665</v>
+        <v>612</v>
       </c>
       <c r="C48" t="n">
-        <v>704</v>
+        <v>673</v>
       </c>
       <c r="D48" t="n">
-        <v>711</v>
+        <v>683</v>
       </c>
       <c r="E48" t="n">
-        <v>598</v>
+        <v>677</v>
       </c>
       <c r="F48" t="n">
-        <v>715</v>
+        <v>671</v>
       </c>
       <c r="G48" t="n">
-        <v>665</v>
+        <v>742</v>
       </c>
       <c r="H48" t="n">
-        <v>640</v>
+        <v>672</v>
       </c>
       <c r="I48" t="n">
-        <v>587</v>
+        <v>672</v>
       </c>
       <c r="J48" t="n">
-        <v>658</v>
+        <v>619</v>
       </c>
       <c r="K48" t="n">
-        <v>651</v>
+        <v>697</v>
       </c>
       <c r="L48" t="n">
-        <v>659.4</v>
+        <v>671.8</v>
       </c>
     </row>
     <row r="49">
@@ -2257,37 +2257,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>783</v>
+        <v>787</v>
       </c>
       <c r="C49" t="n">
-        <v>742</v>
+        <v>831</v>
       </c>
       <c r="D49" t="n">
-        <v>728</v>
+        <v>778</v>
       </c>
       <c r="E49" t="n">
-        <v>777</v>
+        <v>720</v>
       </c>
       <c r="F49" t="n">
-        <v>767</v>
+        <v>868</v>
       </c>
       <c r="G49" t="n">
-        <v>801</v>
+        <v>804</v>
       </c>
       <c r="H49" t="n">
-        <v>726</v>
+        <v>858</v>
       </c>
       <c r="I49" t="n">
-        <v>711</v>
+        <v>736</v>
       </c>
       <c r="J49" t="n">
-        <v>817</v>
+        <v>822</v>
       </c>
       <c r="K49" t="n">
-        <v>870</v>
+        <v>762</v>
       </c>
       <c r="L49" t="n">
-        <v>772.2</v>
+        <v>796.6</v>
       </c>
     </row>
     <row r="50">
@@ -2295,37 +2295,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>732</v>
+        <v>668</v>
       </c>
       <c r="C50" t="n">
-        <v>671</v>
+        <v>633</v>
       </c>
       <c r="D50" t="n">
-        <v>615</v>
+        <v>678</v>
       </c>
       <c r="E50" t="n">
-        <v>704</v>
+        <v>611</v>
       </c>
       <c r="F50" t="n">
-        <v>653</v>
+        <v>626</v>
       </c>
       <c r="G50" t="n">
-        <v>650</v>
+        <v>692</v>
       </c>
       <c r="H50" t="n">
-        <v>684</v>
+        <v>681</v>
       </c>
       <c r="I50" t="n">
-        <v>699</v>
+        <v>692</v>
       </c>
       <c r="J50" t="n">
-        <v>654</v>
+        <v>627</v>
       </c>
       <c r="K50" t="n">
-        <v>662</v>
+        <v>596</v>
       </c>
       <c r="L50" t="n">
-        <v>672.4</v>
+        <v>650.4</v>
       </c>
     </row>
     <row r="51">
@@ -2333,37 +2333,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>643</v>
+        <v>754</v>
       </c>
       <c r="C51" t="n">
-        <v>767</v>
+        <v>719</v>
       </c>
       <c r="D51" t="n">
-        <v>754</v>
+        <v>662</v>
       </c>
       <c r="E51" t="n">
-        <v>622</v>
+        <v>644</v>
       </c>
       <c r="F51" t="n">
-        <v>691</v>
+        <v>641</v>
       </c>
       <c r="G51" t="n">
-        <v>614</v>
+        <v>621</v>
       </c>
       <c r="H51" t="n">
-        <v>664</v>
+        <v>596</v>
       </c>
       <c r="I51" t="n">
-        <v>649</v>
+        <v>692</v>
       </c>
       <c r="J51" t="n">
-        <v>639</v>
+        <v>655</v>
       </c>
       <c r="K51" t="n">
-        <v>671</v>
+        <v>706</v>
       </c>
       <c r="L51" t="n">
-        <v>671.4</v>
+        <v>669</v>
       </c>
     </row>
     <row r="52">
@@ -2373,37 +2373,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>678.4</v>
+        <v>680.26</v>
       </c>
       <c r="C52" t="n">
-        <v>675.72</v>
+        <v>677.52</v>
       </c>
       <c r="D52" t="n">
-        <v>679.54</v>
+        <v>676.6799999999999</v>
       </c>
       <c r="E52" t="n">
-        <v>671.1</v>
+        <v>673.1799999999999</v>
       </c>
       <c r="F52" t="n">
-        <v>690.9</v>
+        <v>666.22</v>
       </c>
       <c r="G52" t="n">
-        <v>673.46</v>
+        <v>677</v>
       </c>
       <c r="H52" t="n">
-        <v>684.46</v>
+        <v>670.66</v>
       </c>
       <c r="I52" t="n">
-        <v>684.04</v>
+        <v>681.3</v>
       </c>
       <c r="J52" t="n">
-        <v>672.78</v>
+        <v>675.58</v>
       </c>
       <c r="K52" t="n">
-        <v>679.4400000000001</v>
+        <v>680.76</v>
       </c>
       <c r="L52" t="n">
-        <v>678.984</v>
+        <v>675.9159999999999</v>
       </c>
     </row>
   </sheetData>
@@ -2462,37 +2462,37 @@
         <v>1</v>
       </c>
       <c r="B2" t="n">
-        <v>4.072613000869751</v>
+        <v>4.067163944244385</v>
       </c>
       <c r="C2" t="n">
-        <v>4.236703157424927</v>
+        <v>4.081612110137939</v>
       </c>
       <c r="D2" t="n">
-        <v>4.169872045516968</v>
+        <v>3.890600204467773</v>
       </c>
       <c r="E2" t="n">
-        <v>4.925971984863281</v>
+        <v>4.675637006759644</v>
       </c>
       <c r="F2" t="n">
-        <v>4.348923683166504</v>
+        <v>4.157894372940063</v>
       </c>
       <c r="G2" t="n">
-        <v>4.318487405776978</v>
+        <v>4.087128162384033</v>
       </c>
       <c r="H2" t="n">
-        <v>4.609265089035034</v>
+        <v>3.923517465591431</v>
       </c>
       <c r="I2" t="n">
-        <v>4.341444253921509</v>
+        <v>3.961921215057373</v>
       </c>
       <c r="J2" t="n">
-        <v>3.995815992355347</v>
+        <v>4.326495885848999</v>
       </c>
       <c r="K2" t="n">
-        <v>4.36888575553894</v>
+        <v>3.989838600158691</v>
       </c>
       <c r="L2" t="n">
-        <v>4.338798236846924</v>
+        <v>4.116180896759033</v>
       </c>
     </row>
     <row r="3">
@@ -2500,37 +2500,37 @@
         <v>10</v>
       </c>
       <c r="B3" t="n">
-        <v>4.598790407180786</v>
+        <v>4.866602897644043</v>
       </c>
       <c r="C3" t="n">
-        <v>4.55638861656189</v>
+        <v>4.565438270568848</v>
       </c>
       <c r="D3" t="n">
-        <v>4.780834436416626</v>
+        <v>4.207303047180176</v>
       </c>
       <c r="E3" t="n">
-        <v>4.581836223602295</v>
+        <v>4.295577049255371</v>
       </c>
       <c r="F3" t="n">
-        <v>4.576350688934326</v>
+        <v>4.477580785751343</v>
       </c>
       <c r="G3" t="n">
-        <v>4.622211933135986</v>
+        <v>4.712515592575073</v>
       </c>
       <c r="H3" t="n">
-        <v>4.367869853973389</v>
+        <v>4.366885185241699</v>
       </c>
       <c r="I3" t="n">
-        <v>4.503036022186279</v>
+        <v>4.606279611587524</v>
       </c>
       <c r="J3" t="n">
-        <v>4.280067443847656</v>
+        <v>4.637177228927612</v>
       </c>
       <c r="K3" t="n">
-        <v>4.797767639160156</v>
+        <v>4.363903760910034</v>
       </c>
       <c r="L3" t="n">
-        <v>4.566515326499939</v>
+        <v>4.509926342964173</v>
       </c>
     </row>
     <row r="4">
@@ -2538,37 +2538,37 @@
         <v>11</v>
       </c>
       <c r="B4" t="n">
-        <v>4.773849487304688</v>
+        <v>4.52398419380188</v>
       </c>
       <c r="C4" t="n">
-        <v>4.955864906311035</v>
+        <v>4.724465131759644</v>
       </c>
       <c r="D4" t="n">
-        <v>4.901455163955688</v>
+        <v>4.572360515594482</v>
       </c>
       <c r="E4" t="n">
-        <v>4.57808256149292</v>
+        <v>4.304548025131226</v>
       </c>
       <c r="F4" t="n">
-        <v>4.485833644866943</v>
+        <v>4.427731037139893</v>
       </c>
       <c r="G4" t="n">
-        <v>4.653875350952148</v>
+        <v>4.672091245651245</v>
       </c>
       <c r="H4" t="n">
-        <v>4.592041015625</v>
+        <v>4.301563739776611</v>
       </c>
       <c r="I4" t="n">
-        <v>4.431448221206665</v>
+        <v>4.760876893997192</v>
       </c>
       <c r="J4" t="n">
-        <v>4.424479246139526</v>
+        <v>4.601321220397949</v>
       </c>
       <c r="K4" t="n">
-        <v>4.557173490524292</v>
+        <v>4.988322973251343</v>
       </c>
       <c r="L4" t="n">
-        <v>4.635410308837891</v>
+        <v>4.587726497650147</v>
       </c>
     </row>
     <row r="5">
@@ -2576,37 +2576,37 @@
         <v>12</v>
       </c>
       <c r="B5" t="n">
-        <v>5.002001047134399</v>
+        <v>4.993793964385986</v>
       </c>
       <c r="C5" t="n">
-        <v>4.918721437454224</v>
+        <v>4.688573598861694</v>
       </c>
       <c r="D5" t="n">
-        <v>5.037874221801758</v>
+        <v>4.584333658218384</v>
       </c>
       <c r="E5" t="n">
-        <v>5.03789496421814</v>
+        <v>5.040177822113037</v>
       </c>
       <c r="F5" t="n">
-        <v>4.94362998008728</v>
+        <v>4.965389013290405</v>
       </c>
       <c r="G5" t="n">
-        <v>5.10424280166626</v>
+        <v>4.776342630386353</v>
       </c>
       <c r="H5" t="n">
-        <v>5.341091394424438</v>
+        <v>5.143475294113159</v>
       </c>
       <c r="I5" t="n">
-        <v>5.290250539779663</v>
+        <v>4.706536054611206</v>
       </c>
       <c r="J5" t="n">
-        <v>4.838917970657349</v>
+        <v>4.827705860137939</v>
       </c>
       <c r="K5" t="n">
-        <v>4.966561555862427</v>
+        <v>5.040170907974243</v>
       </c>
       <c r="L5" t="n">
-        <v>5.048118591308594</v>
+        <v>4.876649880409241</v>
       </c>
     </row>
     <row r="6">
@@ -2614,37 +2614,37 @@
         <v>13</v>
       </c>
       <c r="B6" t="n">
-        <v>3.724303245544434</v>
+        <v>3.744458436965942</v>
       </c>
       <c r="C6" t="n">
-        <v>3.878915309906006</v>
+        <v>3.931518077850342</v>
       </c>
       <c r="D6" t="n">
-        <v>3.619583368301392</v>
+        <v>3.881618976593018</v>
       </c>
       <c r="E6" t="n">
-        <v>3.804085493087769</v>
+        <v>3.719022989273071</v>
       </c>
       <c r="F6" t="n">
-        <v>3.940737962722778</v>
+        <v>3.745961427688599</v>
       </c>
       <c r="G6" t="n">
-        <v>3.857947587966919</v>
+        <v>3.755437612533569</v>
       </c>
       <c r="H6" t="n">
-        <v>4.300476312637329</v>
+        <v>3.739974498748779</v>
       </c>
       <c r="I6" t="n">
-        <v>4.334513902664185</v>
+        <v>3.799340009689331</v>
       </c>
       <c r="J6" t="n">
-        <v>3.572890281677246</v>
+        <v>3.990961790084839</v>
       </c>
       <c r="K6" t="n">
-        <v>4.025744199752808</v>
+        <v>3.771888494491577</v>
       </c>
       <c r="L6" t="n">
-        <v>3.905919766426087</v>
+        <v>3.808018231391907</v>
       </c>
     </row>
     <row r="7">
@@ -2652,37 +2652,37 @@
         <v>14</v>
       </c>
       <c r="B7" t="n">
-        <v>5.464079141616821</v>
+        <v>4.992305040359497</v>
       </c>
       <c r="C7" t="n">
-        <v>4.770867109298706</v>
+        <v>4.742179155349731</v>
       </c>
       <c r="D7" t="n">
-        <v>5.172800302505493</v>
+        <v>4.364656925201416</v>
       </c>
       <c r="E7" t="n">
-        <v>4.556871652603149</v>
+        <v>4.798519849777222</v>
       </c>
       <c r="F7" t="n">
-        <v>5.151955604553223</v>
+        <v>4.974561214447021</v>
       </c>
       <c r="G7" t="n">
-        <v>4.419730663299561</v>
+        <v>4.542824983596802</v>
       </c>
       <c r="H7" t="n">
-        <v>4.810729503631592</v>
+        <v>4.877610206604004</v>
       </c>
       <c r="I7" t="n">
-        <v>4.617215871810913</v>
+        <v>5.041168689727783</v>
       </c>
       <c r="J7" t="n">
-        <v>5.321947813034058</v>
+        <v>4.647863149642944</v>
       </c>
       <c r="K7" t="n">
-        <v>5.420182228088379</v>
+        <v>4.478861570358276</v>
       </c>
       <c r="L7" t="n">
-        <v>4.97063798904419</v>
+        <v>4.74605507850647</v>
       </c>
     </row>
     <row r="8">
@@ -2690,37 +2690,37 @@
         <v>15</v>
       </c>
       <c r="B8" t="n">
-        <v>4.076109886169434</v>
+        <v>3.64457631111145</v>
       </c>
       <c r="C8" t="n">
-        <v>3.779853105545044</v>
+        <v>4.291375398635864</v>
       </c>
       <c r="D8" t="n">
-        <v>4.044193983078003</v>
+        <v>4.077404499053955</v>
       </c>
       <c r="E8" t="n">
-        <v>4.166855573654175</v>
+        <v>3.863463640213013</v>
       </c>
       <c r="F8" t="n">
-        <v>3.931470155715942</v>
+        <v>3.908349990844727</v>
       </c>
       <c r="G8" t="n">
-        <v>4.298536539077759</v>
+        <v>4.036518096923828</v>
       </c>
       <c r="H8" t="n">
-        <v>4.007783651351929</v>
+        <v>4.103850841522217</v>
       </c>
       <c r="I8" t="n">
-        <v>4.061146020889282</v>
+        <v>4.254746675491333</v>
       </c>
       <c r="J8" t="n">
-        <v>3.921509981155396</v>
+        <v>4.242182970046997</v>
       </c>
       <c r="K8" t="n">
-        <v>4.061642646789551</v>
+        <v>3.75495719909668</v>
       </c>
       <c r="L8" t="n">
-        <v>4.034910154342652</v>
+        <v>4.017742562294006</v>
       </c>
     </row>
     <row r="9">
@@ -2728,37 +2728,37 @@
         <v>16</v>
       </c>
       <c r="B9" t="n">
-        <v>3.917497396469116</v>
+        <v>3.754941701889038</v>
       </c>
       <c r="C9" t="n">
-        <v>3.674667835235596</v>
+        <v>3.749477386474609</v>
       </c>
       <c r="D9" t="n">
-        <v>4.11101508140564</v>
+        <v>3.664680004119873</v>
       </c>
       <c r="E9" t="n">
-        <v>3.702075481414795</v>
+        <v>3.808321237564087</v>
       </c>
       <c r="F9" t="n">
-        <v>3.986873865127563</v>
+        <v>3.696165800094604</v>
       </c>
       <c r="G9" t="n">
-        <v>3.775374889373779</v>
+        <v>3.751453876495361</v>
       </c>
       <c r="H9" t="n">
-        <v>3.867124319076538</v>
+        <v>3.474154472351074</v>
       </c>
       <c r="I9" t="n">
-        <v>3.797315120697021</v>
+        <v>4.052252769470215</v>
       </c>
       <c r="J9" t="n">
-        <v>3.940970182418823</v>
+        <v>4.055668115615845</v>
       </c>
       <c r="K9" t="n">
-        <v>4.077596187591553</v>
+        <v>3.519544363021851</v>
       </c>
       <c r="L9" t="n">
-        <v>3.885051035881042</v>
+        <v>3.752665972709656</v>
       </c>
     </row>
     <row r="10">
@@ -2766,37 +2766,37 @@
         <v>17</v>
       </c>
       <c r="B10" t="n">
-        <v>4.467118263244629</v>
+        <v>4.820591449737549</v>
       </c>
       <c r="C10" t="n">
-        <v>4.696513175964355</v>
+        <v>4.671367406845093</v>
       </c>
       <c r="D10" t="n">
-        <v>5.222690343856812</v>
+        <v>4.652894258499146</v>
       </c>
       <c r="E10" t="n">
-        <v>4.812736749649048</v>
+        <v>4.625526666641235</v>
       </c>
       <c r="F10" t="n">
-        <v>5.561320066452026</v>
+        <v>4.96165132522583</v>
       </c>
       <c r="G10" t="n">
-        <v>4.63967490196228</v>
+        <v>4.888784170150757</v>
       </c>
       <c r="H10" t="n">
-        <v>5.165319681167603</v>
+        <v>5.382039308547974</v>
       </c>
       <c r="I10" t="n">
-        <v>5.481525659561157</v>
+        <v>4.758122205734253</v>
       </c>
       <c r="J10" t="n">
-        <v>4.741394758224487</v>
+        <v>5.810053110122681</v>
       </c>
       <c r="K10" t="n">
-        <v>4.891037940979004</v>
+        <v>4.687312602996826</v>
       </c>
       <c r="L10" t="n">
-        <v>4.96793315410614</v>
+        <v>4.925834250450134</v>
       </c>
     </row>
     <row r="11">
@@ -2804,37 +2804,37 @@
         <v>18</v>
       </c>
       <c r="B11" t="n">
-        <v>4.449661016464233</v>
+        <v>4.52476692199707</v>
       </c>
       <c r="C11" t="n">
-        <v>4.641683340072632</v>
+        <v>4.355201005935669</v>
       </c>
       <c r="D11" t="n">
-        <v>4.727454423904419</v>
+        <v>4.762614727020264</v>
       </c>
       <c r="E11" t="n">
-        <v>4.360387563705444</v>
+        <v>4.67935848236084</v>
       </c>
       <c r="F11" t="n">
-        <v>4.2835853099823</v>
+        <v>4.114795446395874</v>
       </c>
       <c r="G11" t="n">
-        <v>4.337454080581665</v>
+        <v>4.559652328491211</v>
       </c>
       <c r="H11" t="n">
-        <v>4.47806715965271</v>
+        <v>4.491316080093384</v>
       </c>
       <c r="I11" t="n">
-        <v>4.740426540374756</v>
+        <v>4.40653133392334</v>
       </c>
       <c r="J11" t="n">
-        <v>4.439198017120361</v>
+        <v>4.285355806350708</v>
       </c>
       <c r="K11" t="n">
-        <v>4.427713871002197</v>
+        <v>4.378113985061646</v>
       </c>
       <c r="L11" t="n">
-        <v>4.488563132286072</v>
+        <v>4.455770611763</v>
       </c>
     </row>
     <row r="12">
@@ -2842,37 +2842,37 @@
         <v>19</v>
       </c>
       <c r="B12" t="n">
-        <v>4.213256359100342</v>
+        <v>3.982130765914917</v>
       </c>
       <c r="C12" t="n">
-        <v>4.157909393310547</v>
+        <v>3.770216941833496</v>
       </c>
       <c r="D12" t="n">
-        <v>3.998842477798462</v>
+        <v>3.999590158462524</v>
       </c>
       <c r="E12" t="n">
-        <v>3.806089162826538</v>
+        <v>4.095890760421753</v>
       </c>
       <c r="F12" t="n">
-        <v>3.8604416847229</v>
+        <v>4.039490938186646</v>
       </c>
       <c r="G12" t="n">
-        <v>3.836006879806519</v>
+        <v>3.827043533325195</v>
       </c>
       <c r="H12" t="n">
-        <v>3.824043035507202</v>
+        <v>4.084098100662231</v>
       </c>
       <c r="I12" t="n">
-        <v>3.805123090744019</v>
+        <v>3.829282283782959</v>
       </c>
       <c r="J12" t="n">
-        <v>3.850979089736938</v>
+        <v>3.910545587539673</v>
       </c>
       <c r="K12" t="n">
-        <v>4.203202247619629</v>
+        <v>3.750455856323242</v>
       </c>
       <c r="L12" t="n">
-        <v>3.955589342117309</v>
+        <v>3.928874492645264</v>
       </c>
     </row>
     <row r="13">
@@ -2880,37 +2880,37 @@
         <v>2</v>
       </c>
       <c r="B13" t="n">
-        <v>3.833517789840698</v>
+        <v>3.899620532989502</v>
       </c>
       <c r="C13" t="n">
-        <v>3.850961685180664</v>
+        <v>3.888657569885254</v>
       </c>
       <c r="D13" t="n">
-        <v>3.791131258010864</v>
+        <v>3.905366659164429</v>
       </c>
       <c r="E13" t="n">
-        <v>3.865921974182129</v>
+        <v>3.833242177963257</v>
       </c>
       <c r="F13" t="n">
-        <v>3.794097900390625</v>
+        <v>3.672636270523071</v>
       </c>
       <c r="G13" t="n">
-        <v>3.734273195266724</v>
+        <v>3.835736274719238</v>
       </c>
       <c r="H13" t="n">
-        <v>4.571606636047363</v>
+        <v>3.876116514205933</v>
       </c>
       <c r="I13" t="n">
-        <v>3.827039957046509</v>
+        <v>3.896585941314697</v>
       </c>
       <c r="J13" t="n">
-        <v>3.960703611373901</v>
+        <v>4.05517840385437</v>
       </c>
       <c r="K13" t="n">
-        <v>3.666454315185547</v>
+        <v>4.222262859344482</v>
       </c>
       <c r="L13" t="n">
-        <v>3.889570832252502</v>
+        <v>3.908540320396424</v>
       </c>
     </row>
     <row r="14">
@@ -2918,37 +2918,37 @@
         <v>20</v>
       </c>
       <c r="B14" t="n">
-        <v>3.792617321014404</v>
+        <v>3.985860347747803</v>
       </c>
       <c r="C14" t="n">
-        <v>3.856894969940186</v>
+        <v>4.295114994049072</v>
       </c>
       <c r="D14" t="n">
-        <v>3.777372598648071</v>
+        <v>3.753483295440674</v>
       </c>
       <c r="E14" t="n">
-        <v>4.278085470199585</v>
+        <v>3.95441722869873</v>
       </c>
       <c r="F14" t="n">
-        <v>4.58830738067627</v>
+        <v>3.849717617034912</v>
       </c>
       <c r="G14" t="n">
-        <v>3.773383140563965</v>
+        <v>4.179855585098267</v>
       </c>
       <c r="H14" t="n">
-        <v>4.207277536392212</v>
+        <v>3.740483522415161</v>
       </c>
       <c r="I14" t="n">
-        <v>4.073632001876831</v>
+        <v>4.234230995178223</v>
       </c>
       <c r="J14" t="n">
-        <v>4.254658937454224</v>
+        <v>4.190338134765625</v>
       </c>
       <c r="K14" t="n">
-        <v>4.382325410842896</v>
+        <v>3.914535760879517</v>
       </c>
       <c r="L14" t="n">
-        <v>4.098455476760864</v>
+        <v>4.009803748130798</v>
       </c>
     </row>
     <row r="15">
@@ -2956,37 +2956,37 @@
         <v>21</v>
       </c>
       <c r="B15" t="n">
-        <v>4.717493534088135</v>
+        <v>4.483438014984131</v>
       </c>
       <c r="C15" t="n">
-        <v>4.659127473831177</v>
+        <v>4.559628009796143</v>
       </c>
       <c r="D15" t="n">
-        <v>4.391796112060547</v>
+        <v>4.350703001022339</v>
       </c>
       <c r="E15" t="n">
-        <v>4.624211549758911</v>
+        <v>4.608100891113281</v>
       </c>
       <c r="F15" t="n">
-        <v>4.395797729492188</v>
+        <v>4.486356973648071</v>
       </c>
       <c r="G15" t="n">
-        <v>4.483086824417114</v>
+        <v>4.411573886871338</v>
       </c>
       <c r="H15" t="n">
-        <v>4.354377269744873</v>
+        <v>4.592055559158325</v>
       </c>
       <c r="I15" t="n">
-        <v>4.233204364776611</v>
+        <v>4.473872423171997</v>
       </c>
       <c r="J15" t="n">
-        <v>4.507003545761108</v>
+        <v>3.995590448379517</v>
       </c>
       <c r="K15" t="n">
-        <v>4.340426921844482</v>
+        <v>4.289350032806396</v>
       </c>
       <c r="L15" t="n">
-        <v>4.470652532577515</v>
+        <v>4.425066924095153</v>
       </c>
     </row>
     <row r="16">
@@ -2994,37 +2994,37 @@
         <v>22</v>
       </c>
       <c r="B16" t="n">
-        <v>4.510026454925537</v>
+        <v>4.052469253540039</v>
       </c>
       <c r="C16" t="n">
-        <v>4.14294171333313</v>
+        <v>4.90576434135437</v>
       </c>
       <c r="D16" t="n">
-        <v>4.17436671257019</v>
+        <v>4.235987663269043</v>
       </c>
       <c r="E16" t="n">
-        <v>4.282075166702271</v>
+        <v>3.960710525512695</v>
       </c>
       <c r="F16" t="n">
-        <v>4.251671075820923</v>
+        <v>4.101842164993286</v>
       </c>
       <c r="G16" t="n">
-        <v>3.968358278274536</v>
+        <v>4.110803365707397</v>
       </c>
       <c r="H16" t="n">
-        <v>4.81873083114624</v>
+        <v>4.091888427734375</v>
       </c>
       <c r="I16" t="n">
-        <v>4.277603387832642</v>
+        <v>4.478368997573853</v>
       </c>
       <c r="J16" t="n">
-        <v>3.957907438278198</v>
+        <v>4.013549566268921</v>
       </c>
       <c r="K16" t="n">
-        <v>4.32846212387085</v>
+        <v>3.81708025932312</v>
       </c>
       <c r="L16" t="n">
-        <v>4.271214318275452</v>
+        <v>4.17684645652771</v>
       </c>
     </row>
     <row r="17">
@@ -3032,37 +3032,37 @@
         <v>23</v>
       </c>
       <c r="B17" t="n">
-        <v>4.156891345977783</v>
+        <v>4.300811290740967</v>
       </c>
       <c r="C17" t="n">
-        <v>4.139466762542725</v>
+        <v>4.243469715118408</v>
       </c>
       <c r="D17" t="n">
-        <v>4.608772754669189</v>
+        <v>4.3272545337677</v>
       </c>
       <c r="E17" t="n">
-        <v>4.384808540344238</v>
+        <v>4.119770765304565</v>
       </c>
       <c r="F17" t="n">
-        <v>4.485082626342773</v>
+        <v>4.569140434265137</v>
       </c>
       <c r="G17" t="n">
-        <v>4.219254970550537</v>
+        <v>4.451426029205322</v>
       </c>
       <c r="H17" t="n">
-        <v>4.26164174079895</v>
+        <v>4.476862907409668</v>
       </c>
       <c r="I17" t="n">
-        <v>4.382321357727051</v>
+        <v>4.21104884147644</v>
       </c>
       <c r="J17" t="n">
-        <v>4.618233919143677</v>
+        <v>4.156675815582275</v>
       </c>
       <c r="K17" t="n">
-        <v>4.55339527130127</v>
+        <v>4.331737756729126</v>
       </c>
       <c r="L17" t="n">
-        <v>4.380986928939819</v>
+        <v>4.318819808959961</v>
       </c>
     </row>
     <row r="18">
@@ -3070,37 +3070,37 @@
         <v>24</v>
       </c>
       <c r="B18" t="n">
-        <v>3.686115741729736</v>
+        <v>3.589219331741333</v>
       </c>
       <c r="C18" t="n">
-        <v>3.946422338485718</v>
+        <v>3.880408525466919</v>
       </c>
       <c r="D18" t="n">
-        <v>3.620781898498535</v>
+        <v>3.806119918823242</v>
       </c>
       <c r="E18" t="n">
-        <v>4.00577712059021</v>
+        <v>3.714837551116943</v>
       </c>
       <c r="F18" t="n">
-        <v>3.869661331176758</v>
+        <v>3.970683336257935</v>
       </c>
       <c r="G18" t="n">
-        <v>3.562429666519165</v>
+        <v>3.751750230789185</v>
       </c>
       <c r="H18" t="n">
-        <v>3.690085887908936</v>
+        <v>3.576714992523193</v>
       </c>
       <c r="I18" t="n">
-        <v>3.827245950698853</v>
+        <v>3.906672954559326</v>
       </c>
       <c r="J18" t="n">
-        <v>3.678117990493774</v>
+        <v>3.668954610824585</v>
       </c>
       <c r="K18" t="n">
-        <v>3.883585929870605</v>
+        <v>3.688406467437744</v>
       </c>
       <c r="L18" t="n">
-        <v>3.777022385597229</v>
+        <v>3.755376791954041</v>
       </c>
     </row>
     <row r="19">
@@ -3108,37 +3108,37 @@
         <v>25</v>
       </c>
       <c r="B19" t="n">
-        <v>4.435902118682861</v>
+        <v>4.682345390319824</v>
       </c>
       <c r="C19" t="n">
-        <v>4.308273553848267</v>
+        <v>4.631938219070435</v>
       </c>
       <c r="D19" t="n">
-        <v>4.556137323379517</v>
+        <v>4.31328821182251</v>
       </c>
       <c r="E19" t="n">
-        <v>4.507305383682251</v>
+        <v>4.408532857894897</v>
       </c>
       <c r="F19" t="n">
-        <v>4.393557071685791</v>
+        <v>4.565129518508911</v>
       </c>
       <c r="G19" t="n">
-        <v>4.19009256362915</v>
+        <v>4.225009679794312</v>
       </c>
       <c r="H19" t="n">
-        <v>4.338200330734253</v>
+        <v>4.508777618408203</v>
       </c>
       <c r="I19" t="n">
-        <v>4.331750392913818</v>
+        <v>4.299347162246704</v>
       </c>
       <c r="J19" t="n">
-        <v>4.372107744216919</v>
+        <v>4.325303316116333</v>
       </c>
       <c r="K19" t="n">
-        <v>4.313268423080444</v>
+        <v>4.377634763717651</v>
       </c>
       <c r="L19" t="n">
-        <v>4.374659490585327</v>
+        <v>4.433730673789978</v>
       </c>
     </row>
     <row r="20">
@@ -3146,37 +3146,37 @@
         <v>26</v>
       </c>
       <c r="B20" t="n">
-        <v>4.384573221206665</v>
+        <v>4.173871994018555</v>
       </c>
       <c r="C20" t="n">
-        <v>4.088891744613647</v>
+        <v>4.237985610961914</v>
       </c>
       <c r="D20" t="n">
-        <v>3.980663299560547</v>
+        <v>4.123825311660767</v>
       </c>
       <c r="E20" t="n">
-        <v>4.132749795913696</v>
+        <v>4.185115575790405</v>
       </c>
       <c r="F20" t="n">
-        <v>4.386615753173828</v>
+        <v>4.138747692108154</v>
       </c>
       <c r="G20" t="n">
-        <v>3.950197458267212</v>
+        <v>4.228013038635254</v>
       </c>
       <c r="H20" t="n">
-        <v>4.06290864944458</v>
+        <v>3.993606567382812</v>
       </c>
       <c r="I20" t="n">
-        <v>4.563637733459473</v>
+        <v>4.201112270355225</v>
       </c>
       <c r="J20" t="n">
-        <v>4.117799758911133</v>
+        <v>3.941253662109375</v>
       </c>
       <c r="K20" t="n">
-        <v>4.248454809188843</v>
+        <v>4.161171436309814</v>
       </c>
       <c r="L20" t="n">
-        <v>4.191649222373963</v>
+        <v>4.138470315933228</v>
       </c>
     </row>
     <row r="21">
@@ -3184,37 +3184,37 @@
         <v>27</v>
       </c>
       <c r="B21" t="n">
-        <v>4.034483671188354</v>
+        <v>4.456951379776001</v>
       </c>
       <c r="C21" t="n">
-        <v>4.172152280807495</v>
+        <v>4.081368923187256</v>
       </c>
       <c r="D21" t="n">
-        <v>4.028311491012573</v>
+        <v>4.317978143692017</v>
       </c>
       <c r="E21" t="n">
-        <v>4.421717166900635</v>
+        <v>4.568119764328003</v>
       </c>
       <c r="F21" t="n">
-        <v>4.093072414398193</v>
+        <v>4.098852157592773</v>
       </c>
       <c r="G21" t="n">
-        <v>4.283576011657715</v>
+        <v>4.621980428695679</v>
       </c>
       <c r="H21" t="n">
-        <v>4.129962205886841</v>
+        <v>4.413003206253052</v>
       </c>
       <c r="I21" t="n">
-        <v>3.955411434173584</v>
+        <v>4.354423999786377</v>
       </c>
       <c r="J21" t="n">
-        <v>4.112010717391968</v>
+        <v>4.318053007125854</v>
       </c>
       <c r="K21" t="n">
-        <v>4.19431734085083</v>
+        <v>4.260141611099243</v>
       </c>
       <c r="L21" t="n">
-        <v>4.142501473426819</v>
+        <v>4.349087262153626</v>
       </c>
     </row>
     <row r="22">
@@ -3222,37 +3222,37 @@
         <v>28</v>
       </c>
       <c r="B22" t="n">
-        <v>4.242173671722412</v>
+        <v>4.247688770294189</v>
       </c>
       <c r="C22" t="n">
-        <v>4.129498958587646</v>
+        <v>3.898198127746582</v>
       </c>
       <c r="D22" t="n">
-        <v>4.128963470458984</v>
+        <v>4.213731288909912</v>
       </c>
       <c r="E22" t="n">
-        <v>4.153897047042847</v>
+        <v>3.949718475341797</v>
       </c>
       <c r="F22" t="n">
-        <v>4.189322233200073</v>
+        <v>4.401577949523926</v>
       </c>
       <c r="G22" t="n">
-        <v>3.934464693069458</v>
+        <v>3.837024688720703</v>
       </c>
       <c r="H22" t="n">
-        <v>4.120007276535034</v>
+        <v>4.290362358093262</v>
       </c>
       <c r="I22" t="n">
-        <v>4.099041938781738</v>
+        <v>4.252984523773193</v>
       </c>
       <c r="J22" t="n">
-        <v>4.36187744140625</v>
+        <v>4.211520433425903</v>
       </c>
       <c r="K22" t="n">
-        <v>3.928471565246582</v>
+        <v>4.436207056045532</v>
       </c>
       <c r="L22" t="n">
-        <v>4.128771829605102</v>
+        <v>4.1739013671875</v>
       </c>
     </row>
     <row r="23">
@@ -3260,37 +3260,37 @@
         <v>29</v>
       </c>
       <c r="B23" t="n">
-        <v>4.311522483825684</v>
+        <v>4.180854320526123</v>
       </c>
       <c r="C23" t="n">
-        <v>4.330509424209595</v>
+        <v>4.287580966949463</v>
       </c>
       <c r="D23" t="n">
-        <v>4.089075565338135</v>
+        <v>4.063177824020386</v>
       </c>
       <c r="E23" t="n">
-        <v>4.186311721801758</v>
+        <v>4.46862006187439</v>
       </c>
       <c r="F23" t="n">
-        <v>4.240173816680908</v>
+        <v>4.024758100509644</v>
       </c>
       <c r="G23" t="n">
-        <v>4.516071557998657</v>
+        <v>4.129997730255127</v>
       </c>
       <c r="H23" t="n">
-        <v>4.485084056854248</v>
+        <v>4.607276439666748</v>
       </c>
       <c r="I23" t="n">
-        <v>4.052664995193481</v>
+        <v>4.196316003799438</v>
       </c>
       <c r="J23" t="n">
-        <v>4.41473388671875</v>
+        <v>4.203813552856445</v>
       </c>
       <c r="K23" t="n">
-        <v>4.772836208343506</v>
+        <v>3.989337682723999</v>
       </c>
       <c r="L23" t="n">
-        <v>4.339898371696473</v>
+        <v>4.215173268318177</v>
       </c>
     </row>
     <row r="24">
@@ -3298,37 +3298,37 @@
         <v>3</v>
       </c>
       <c r="B24" t="n">
-        <v>4.07212233543396</v>
+        <v>4.251700162887573</v>
       </c>
       <c r="C24" t="n">
-        <v>4.388329029083252</v>
+        <v>4.920047998428345</v>
       </c>
       <c r="D24" t="n">
-        <v>4.092077970504761</v>
+        <v>3.991864204406738</v>
       </c>
       <c r="E24" t="n">
-        <v>3.962896347045898</v>
+        <v>4.32249116897583</v>
       </c>
       <c r="F24" t="n">
-        <v>4.433133602142334</v>
+        <v>3.74994945526123</v>
       </c>
       <c r="G24" t="n">
-        <v>4.519756555557251</v>
+        <v>4.169421672821045</v>
       </c>
       <c r="H24" t="n">
-        <v>3.89136266708374</v>
+        <v>3.922512292861938</v>
       </c>
       <c r="I24" t="n">
-        <v>4.630951404571533</v>
+        <v>4.249188899993896</v>
       </c>
       <c r="J24" t="n">
-        <v>4.232966899871826</v>
+        <v>4.394811153411865</v>
       </c>
       <c r="K24" t="n">
-        <v>4.156182527542114</v>
+        <v>3.888606786727905</v>
       </c>
       <c r="L24" t="n">
-        <v>4.237977933883667</v>
+        <v>4.186059379577637</v>
       </c>
     </row>
     <row r="25">
@@ -3336,37 +3336,37 @@
         <v>30</v>
       </c>
       <c r="B25" t="n">
-        <v>3.873434066772461</v>
+        <v>3.606845617294312</v>
       </c>
       <c r="C25" t="n">
-        <v>3.699851036071777</v>
+        <v>3.8497314453125</v>
       </c>
       <c r="D25" t="n">
-        <v>3.850973606109619</v>
+        <v>3.766907215118408</v>
       </c>
       <c r="E25" t="n">
-        <v>3.734288215637207</v>
+        <v>3.913550138473511</v>
       </c>
       <c r="F25" t="n">
-        <v>3.684412717819214</v>
+        <v>3.577881813049316</v>
       </c>
       <c r="G25" t="n">
-        <v>3.728803157806396</v>
+        <v>3.758443355560303</v>
       </c>
       <c r="H25" t="n">
-        <v>3.716337919235229</v>
+        <v>3.643772602081299</v>
       </c>
       <c r="I25" t="n">
-        <v>3.60309100151062</v>
+        <v>3.846206426620483</v>
       </c>
       <c r="J25" t="n">
-        <v>3.888401508331299</v>
+        <v>3.996822118759155</v>
       </c>
       <c r="K25" t="n">
-        <v>3.800104141235352</v>
+        <v>3.671159505844116</v>
       </c>
       <c r="L25" t="n">
-        <v>3.757969737052917</v>
+        <v>3.76313202381134</v>
       </c>
     </row>
     <row r="26">
@@ -3374,37 +3374,37 @@
         <v>31</v>
       </c>
       <c r="B26" t="n">
-        <v>4.417484760284424</v>
+        <v>4.253703832626343</v>
       </c>
       <c r="C26" t="n">
-        <v>4.634440660476685</v>
+        <v>4.640184164047241</v>
       </c>
       <c r="D26" t="n">
-        <v>4.518731355667114</v>
+        <v>4.436698436737061</v>
       </c>
       <c r="E26" t="n">
-        <v>4.487830400466919</v>
+        <v>4.279597520828247</v>
       </c>
       <c r="F26" t="n">
-        <v>4.479332685470581</v>
+        <v>4.353931188583374</v>
       </c>
       <c r="G26" t="n">
-        <v>4.378607273101807</v>
+        <v>4.338481426239014</v>
       </c>
       <c r="H26" t="n">
-        <v>4.265220165252686</v>
+        <v>4.530954599380493</v>
       </c>
       <c r="I26" t="n">
-        <v>4.700539827346802</v>
+        <v>4.654678821563721</v>
       </c>
       <c r="J26" t="n">
-        <v>4.730933427810669</v>
+        <v>4.505065679550171</v>
       </c>
       <c r="K26" t="n">
-        <v>4.691040277481079</v>
+        <v>4.60775351524353</v>
       </c>
       <c r="L26" t="n">
-        <v>4.530416083335877</v>
+        <v>4.460104918479919</v>
       </c>
     </row>
     <row r="27">
@@ -3412,37 +3412,37 @@
         <v>32</v>
       </c>
       <c r="B27" t="n">
-        <v>4.800246715545654</v>
+        <v>4.591801166534424</v>
       </c>
       <c r="C27" t="n">
-        <v>4.667640924453735</v>
+        <v>4.617239952087402</v>
       </c>
       <c r="D27" t="n">
-        <v>4.841656446456909</v>
+        <v>4.694603443145752</v>
       </c>
       <c r="E27" t="n">
-        <v>4.467108488082886</v>
+        <v>4.5020432472229</v>
       </c>
       <c r="F27" t="n">
-        <v>4.965845823287964</v>
+        <v>4.410768032073975</v>
       </c>
       <c r="G27" t="n">
-        <v>4.917940855026245</v>
+        <v>4.475109100341797</v>
       </c>
       <c r="H27" t="n">
-        <v>4.612227439880371</v>
+        <v>4.320484638214111</v>
       </c>
       <c r="I27" t="n">
-        <v>4.854158639907837</v>
+        <v>4.591316699981689</v>
       </c>
       <c r="J27" t="n">
-        <v>4.714474678039551</v>
+        <v>4.383869647979736</v>
       </c>
       <c r="K27" t="n">
-        <v>4.487057685852051</v>
+        <v>4.475594520568848</v>
       </c>
       <c r="L27" t="n">
-        <v>4.73283576965332</v>
+        <v>4.506283044815063</v>
       </c>
     </row>
     <row r="28">
@@ -3450,37 +3450,37 @@
         <v>33</v>
       </c>
       <c r="B28" t="n">
-        <v>4.009786605834961</v>
+        <v>4.021764278411865</v>
       </c>
       <c r="C28" t="n">
-        <v>4.564846038818359</v>
+        <v>4.14746618270874</v>
       </c>
       <c r="D28" t="n">
-        <v>3.975908517837524</v>
+        <v>3.963394641876221</v>
       </c>
       <c r="E28" t="n">
-        <v>3.968910217285156</v>
+        <v>3.920529127120972</v>
       </c>
       <c r="F28" t="n">
-        <v>4.099534511566162</v>
+        <v>3.895602226257324</v>
       </c>
       <c r="G28" t="n">
-        <v>4.00778341293335</v>
+        <v>3.9215087890625</v>
       </c>
       <c r="H28" t="n">
-        <v>3.908543825149536</v>
+        <v>4.17039155960083</v>
       </c>
       <c r="I28" t="n">
-        <v>3.952937602996826</v>
+        <v>3.926524639129639</v>
       </c>
       <c r="J28" t="n">
-        <v>4.281592845916748</v>
+        <v>4.172409296035767</v>
       </c>
       <c r="K28" t="n">
-        <v>3.967365264892578</v>
+        <v>3.978880405426025</v>
       </c>
       <c r="L28" t="n">
-        <v>4.07372088432312</v>
+        <v>4.011847114562988</v>
       </c>
     </row>
     <row r="29">
@@ -3488,37 +3488,37 @@
         <v>34</v>
       </c>
       <c r="B29" t="n">
-        <v>4.204294681549072</v>
+        <v>4.075605630874634</v>
       </c>
       <c r="C29" t="n">
-        <v>4.31549596786499</v>
+        <v>4.211297750473022</v>
       </c>
       <c r="D29" t="n">
-        <v>4.398800373077393</v>
+        <v>4.440070629119873</v>
       </c>
       <c r="E29" t="n">
-        <v>4.171372652053833</v>
+        <v>4.321288108825684</v>
       </c>
       <c r="F29" t="n">
-        <v>4.163913488388062</v>
+        <v>4.064438581466675</v>
       </c>
       <c r="G29" t="n">
-        <v>4.169376134872437</v>
+        <v>4.283366918563843</v>
       </c>
       <c r="H29" t="n">
-        <v>4.527939558029175</v>
+        <v>4.522731781005859</v>
       </c>
       <c r="I29" t="n">
-        <v>4.402764558792114</v>
+        <v>4.320272445678711</v>
       </c>
       <c r="J29" t="n">
-        <v>4.26263952255249</v>
+        <v>4.096838474273682</v>
       </c>
       <c r="K29" t="n">
-        <v>4.084582090377808</v>
+        <v>4.069914102554321</v>
       </c>
       <c r="L29" t="n">
-        <v>4.270117902755738</v>
+        <v>4.24058244228363</v>
       </c>
     </row>
     <row r="30">
@@ -3526,37 +3526,37 @@
         <v>35</v>
       </c>
       <c r="B30" t="n">
-        <v>3.885598421096802</v>
+        <v>4.229051113128662</v>
       </c>
       <c r="C30" t="n">
-        <v>3.941437482833862</v>
+        <v>3.952207803726196</v>
       </c>
       <c r="D30" t="n">
-        <v>3.994828939437866</v>
+        <v>3.961705923080444</v>
       </c>
       <c r="E30" t="n">
-        <v>4.225222587585449</v>
+        <v>4.009569644927979</v>
       </c>
       <c r="F30" t="n">
-        <v>4.222722053527832</v>
+        <v>3.929277420043945</v>
       </c>
       <c r="G30" t="n">
-        <v>4.46740460395813</v>
+        <v>3.927299976348877</v>
       </c>
       <c r="H30" t="n">
-        <v>4.657636404037476</v>
+        <v>3.894376993179321</v>
       </c>
       <c r="I30" t="n">
-        <v>4.332444429397583</v>
+        <v>4.21303653717041</v>
       </c>
       <c r="J30" t="n">
-        <v>3.988838195800781</v>
+        <v>3.947746276855469</v>
       </c>
       <c r="K30" t="n">
-        <v>4.039684534072876</v>
+        <v>3.828048467636108</v>
       </c>
       <c r="L30" t="n">
-        <v>4.175581765174866</v>
+        <v>3.989232015609741</v>
       </c>
     </row>
     <row r="31">
@@ -3564,37 +3564,37 @@
         <v>36</v>
       </c>
       <c r="B31" t="n">
-        <v>3.653684854507446</v>
+        <v>3.899397373199463</v>
       </c>
       <c r="C31" t="n">
-        <v>3.845690488815308</v>
+        <v>3.838002443313599</v>
       </c>
       <c r="D31" t="n">
-        <v>3.836215972900391</v>
+        <v>3.882404565811157</v>
       </c>
       <c r="E31" t="n">
-        <v>3.910519361495972</v>
+        <v>3.814118385314941</v>
       </c>
       <c r="F31" t="n">
-        <v>3.806297302246094</v>
+        <v>4.134768962860107</v>
       </c>
       <c r="G31" t="n">
-        <v>3.955416202545166</v>
+        <v>3.727822542190552</v>
       </c>
       <c r="H31" t="n">
-        <v>3.947967767715454</v>
+        <v>3.976694822311401</v>
       </c>
       <c r="I31" t="n">
-        <v>4.068601369857788</v>
+        <v>4.504793882369995</v>
       </c>
       <c r="J31" t="n">
-        <v>3.844717502593994</v>
+        <v>4.362679719924927</v>
       </c>
       <c r="K31" t="n">
-        <v>3.795318365097046</v>
+        <v>3.792625427246094</v>
       </c>
       <c r="L31" t="n">
-        <v>3.866442918777466</v>
+        <v>3.993330812454224</v>
       </c>
     </row>
     <row r="32">
@@ -3602,37 +3602,37 @@
         <v>37</v>
       </c>
       <c r="B32" t="n">
-        <v>4.673068284988403</v>
+        <v>3.940309286117554</v>
       </c>
       <c r="C32" t="n">
-        <v>4.078137159347534</v>
+        <v>4.095856428146362</v>
       </c>
       <c r="D32" t="n">
-        <v>4.11500883102417</v>
+        <v>3.881885528564453</v>
       </c>
       <c r="E32" t="n">
-        <v>4.131959915161133</v>
+        <v>4.364740610122681</v>
       </c>
       <c r="F32" t="n">
-        <v>4.041202306747437</v>
+        <v>4.656660795211792</v>
       </c>
       <c r="G32" t="n">
-        <v>4.49254846572876</v>
+        <v>4.734469175338745</v>
       </c>
       <c r="H32" t="n">
-        <v>3.929983139038086</v>
+        <v>3.908557176589966</v>
       </c>
       <c r="I32" t="n">
-        <v>4.030723094940186</v>
+        <v>3.685129404067993</v>
       </c>
       <c r="J32" t="n">
-        <v>3.768891334533691</v>
+        <v>3.728005170822144</v>
       </c>
       <c r="K32" t="n">
-        <v>3.86864185333252</v>
+        <v>4.410784006118774</v>
       </c>
       <c r="L32" t="n">
-        <v>4.113016438484192</v>
+        <v>4.140639758110046</v>
       </c>
     </row>
     <row r="33">
@@ -3640,37 +3640,37 @@
         <v>38</v>
       </c>
       <c r="B33" t="n">
-        <v>4.7244553565979</v>
+        <v>4.341448545455933</v>
       </c>
       <c r="C33" t="n">
-        <v>4.470120429992676</v>
+        <v>4.890071868896484</v>
       </c>
       <c r="D33" t="n">
-        <v>4.483611345291138</v>
+        <v>4.966866731643677</v>
       </c>
       <c r="E33" t="n">
-        <v>4.966331005096436</v>
+        <v>4.501054048538208</v>
       </c>
       <c r="F33" t="n">
-        <v>4.851625680923462</v>
+        <v>4.184351921081543</v>
       </c>
       <c r="G33" t="n">
-        <v>5.140928745269775</v>
+        <v>4.559410572052002</v>
       </c>
       <c r="H33" t="n">
-        <v>4.300525188446045</v>
+        <v>4.273094892501831</v>
       </c>
       <c r="I33" t="n">
-        <v>4.371387004852295</v>
+        <v>4.466124534606934</v>
       </c>
       <c r="J33" t="n">
-        <v>4.501009464263916</v>
+        <v>4.639200210571289</v>
       </c>
       <c r="K33" t="n">
-        <v>4.684558629989624</v>
+        <v>4.70255446434021</v>
       </c>
       <c r="L33" t="n">
-        <v>4.649455285072326</v>
+        <v>4.552417778968811</v>
       </c>
     </row>
     <row r="34">
@@ -3678,37 +3678,37 @@
         <v>39</v>
       </c>
       <c r="B34" t="n">
-        <v>3.893569946289062</v>
+        <v>3.73303747177124</v>
       </c>
       <c r="C34" t="n">
-        <v>3.518521547317505</v>
+        <v>3.819358110427856</v>
       </c>
       <c r="D34" t="n">
-        <v>3.992813348770142</v>
+        <v>4.074124097824097</v>
       </c>
       <c r="E34" t="n">
-        <v>3.747928857803345</v>
+        <v>3.745966672897339</v>
       </c>
       <c r="F34" t="n">
-        <v>3.860168218612671</v>
+        <v>4.013308525085449</v>
       </c>
       <c r="G34" t="n">
-        <v>3.899563550949097</v>
+        <v>3.663687705993652</v>
       </c>
       <c r="H34" t="n">
-        <v>4.219240427017212</v>
+        <v>3.559937238693237</v>
       </c>
       <c r="I34" t="n">
-        <v>3.775376558303833</v>
+        <v>3.711052656173706</v>
       </c>
       <c r="J34" t="n">
-        <v>3.640744209289551</v>
+        <v>3.527538061141968</v>
       </c>
       <c r="K34" t="n">
-        <v>3.986852884292603</v>
+        <v>3.675132989883423</v>
       </c>
       <c r="L34" t="n">
-        <v>3.853477954864502</v>
+        <v>3.752314352989197</v>
       </c>
     </row>
     <row r="35">
@@ -3716,37 +3716,37 @@
         <v>4</v>
       </c>
       <c r="B35" t="n">
-        <v>4.527484178543091</v>
+        <v>5.122506141662598</v>
       </c>
       <c r="C35" t="n">
-        <v>4.742392301559448</v>
+        <v>4.808824300765991</v>
       </c>
       <c r="D35" t="n">
-        <v>4.879065752029419</v>
+        <v>5.053129434585571</v>
       </c>
       <c r="E35" t="n">
-        <v>4.701529741287231</v>
+        <v>4.932952642440796</v>
       </c>
       <c r="F35" t="n">
-        <v>4.901490211486816</v>
+        <v>4.667827844619751</v>
       </c>
       <c r="G35" t="n">
-        <v>4.850129127502441</v>
+        <v>4.77259349822998</v>
       </c>
       <c r="H35" t="n">
-        <v>4.635191917419434</v>
+        <v>4.855370998382568</v>
       </c>
       <c r="I35" t="n">
-        <v>4.571342945098877</v>
+        <v>4.713248729705811</v>
       </c>
       <c r="J35" t="n">
-        <v>5.31892991065979</v>
+        <v>5.0348961353302</v>
       </c>
       <c r="K35" t="n">
-        <v>4.630197525024414</v>
+        <v>4.575141906738281</v>
       </c>
       <c r="L35" t="n">
-        <v>4.775775361061096</v>
+        <v>4.853649163246155</v>
       </c>
     </row>
     <row r="36">
@@ -3754,37 +3754,37 @@
         <v>40</v>
       </c>
       <c r="B36" t="n">
-        <v>3.421271800994873</v>
+        <v>3.359512567520142</v>
       </c>
       <c r="C36" t="n">
-        <v>3.480627298355103</v>
+        <v>3.595337152481079</v>
       </c>
       <c r="D36" t="n">
-        <v>3.415286540985107</v>
+        <v>3.340828657150269</v>
       </c>
       <c r="E36" t="n">
-        <v>3.624783515930176</v>
+        <v>3.827060699462891</v>
       </c>
       <c r="F36" t="n">
-        <v>3.553442716598511</v>
+        <v>3.562735319137573</v>
       </c>
       <c r="G36" t="n">
-        <v>3.547956228256226</v>
+        <v>3.443037748336792</v>
       </c>
       <c r="H36" t="n">
-        <v>3.577423810958862</v>
+        <v>3.528338432312012</v>
       </c>
       <c r="I36" t="n">
-        <v>3.38138484954834</v>
+        <v>3.540282964706421</v>
       </c>
       <c r="J36" t="n">
-        <v>3.442729949951172</v>
+        <v>3.626103639602661</v>
       </c>
       <c r="K36" t="n">
-        <v>3.387841701507568</v>
+        <v>3.410145282745361</v>
       </c>
       <c r="L36" t="n">
-        <v>3.483274841308594</v>
+        <v>3.52333824634552</v>
       </c>
     </row>
     <row r="37">
@@ -3792,37 +3792,37 @@
         <v>41</v>
       </c>
       <c r="B37" t="n">
-        <v>4.229754447937012</v>
+        <v>4.660876512527466</v>
       </c>
       <c r="C37" t="n">
-        <v>4.623224496841431</v>
+        <v>4.333754777908325</v>
       </c>
       <c r="D37" t="n">
-        <v>4.301525831222534</v>
+        <v>4.283340692520142</v>
       </c>
       <c r="E37" t="n">
-        <v>4.366991758346558</v>
+        <v>4.218266487121582</v>
       </c>
       <c r="F37" t="n">
-        <v>4.311521291732788</v>
+        <v>4.368866682052612</v>
       </c>
       <c r="G37" t="n">
-        <v>4.264626502990723</v>
+        <v>4.26465106010437</v>
       </c>
       <c r="H37" t="n">
-        <v>4.346421003341675</v>
+        <v>4.497060775756836</v>
       </c>
       <c r="I37" t="n">
-        <v>4.190334320068359</v>
+        <v>4.518986225128174</v>
       </c>
       <c r="J37" t="n">
-        <v>4.501044273376465</v>
+        <v>4.436727523803711</v>
       </c>
       <c r="K37" t="n">
-        <v>4.101053714752197</v>
+        <v>4.244183778762817</v>
       </c>
       <c r="L37" t="n">
-        <v>4.323649764060974</v>
+        <v>4.382671451568603</v>
       </c>
     </row>
     <row r="38">
@@ -3830,37 +3830,37 @@
         <v>42</v>
       </c>
       <c r="B38" t="n">
-        <v>4.423723697662354</v>
+        <v>4.540456771850586</v>
       </c>
       <c r="C38" t="n">
-        <v>5.706001281738281</v>
+        <v>4.217258214950562</v>
       </c>
       <c r="D38" t="n">
-        <v>4.642904281616211</v>
+        <v>4.319515943527222</v>
       </c>
       <c r="E38" t="n">
-        <v>4.308277130126953</v>
+        <v>4.59929347038269</v>
       </c>
       <c r="F38" t="n">
-        <v>4.168158769607544</v>
+        <v>4.34843373298645</v>
       </c>
       <c r="G38" t="n">
-        <v>4.716234683990479</v>
+        <v>4.7294602394104</v>
       </c>
       <c r="H38" t="n">
-        <v>4.66285228729248</v>
+        <v>4.467134714126587</v>
       </c>
       <c r="I38" t="n">
-        <v>4.416499853134155</v>
+        <v>4.108060359954834</v>
       </c>
       <c r="J38" t="n">
-        <v>4.798503637313843</v>
+        <v>4.138961791992188</v>
       </c>
       <c r="K38" t="n">
-        <v>4.699266910552979</v>
+        <v>4.885139226913452</v>
       </c>
       <c r="L38" t="n">
-        <v>4.654242253303527</v>
+        <v>4.435371446609497</v>
       </c>
     </row>
     <row r="39">
@@ -3868,37 +3868,37 @@
         <v>43</v>
       </c>
       <c r="B39" t="n">
-        <v>3.843003988265991</v>
+        <v>3.837270975112915</v>
       </c>
       <c r="C39" t="n">
-        <v>4.116100549697876</v>
+        <v>3.767414569854736</v>
       </c>
       <c r="D39" t="n">
-        <v>3.829742670059204</v>
+        <v>3.950450658798218</v>
       </c>
       <c r="E39" t="n">
-        <v>3.923497200012207</v>
+        <v>3.954324960708618</v>
       </c>
       <c r="F39" t="n">
-        <v>3.852173328399658</v>
+        <v>3.642522573471069</v>
       </c>
       <c r="G39" t="n">
-        <v>3.754425048828125</v>
+        <v>3.55308723449707</v>
       </c>
       <c r="H39" t="n">
-        <v>3.860152006149292</v>
+        <v>4.065698146820068</v>
       </c>
       <c r="I39" t="n">
-        <v>3.823242425918579</v>
+        <v>3.731017589569092</v>
       </c>
       <c r="J39" t="n">
-        <v>3.871637105941772</v>
+        <v>3.743485689163208</v>
       </c>
       <c r="K39" t="n">
-        <v>3.89157772064209</v>
+        <v>3.721035003662109</v>
       </c>
       <c r="L39" t="n">
-        <v>3.876555204391479</v>
+        <v>3.79663074016571</v>
       </c>
     </row>
     <row r="40">
@@ -3906,37 +3906,37 @@
         <v>44</v>
       </c>
       <c r="B40" t="n">
-        <v>4.237207889556885</v>
+        <v>4.338470458984375</v>
       </c>
       <c r="C40" t="n">
-        <v>4.317499876022339</v>
+        <v>4.285604953765869</v>
       </c>
       <c r="D40" t="n">
-        <v>4.304513692855835</v>
+        <v>4.143451690673828</v>
       </c>
       <c r="E40" t="n">
-        <v>4.402782201766968</v>
+        <v>4.223253011703491</v>
       </c>
       <c r="F40" t="n">
-        <v>4.669587850570679</v>
+        <v>4.112026691436768</v>
       </c>
       <c r="G40" t="n">
-        <v>4.672079801559448</v>
+        <v>4.241199016571045</v>
       </c>
       <c r="H40" t="n">
-        <v>4.735968828201294</v>
+        <v>4.213269472122192</v>
       </c>
       <c r="I40" t="n">
-        <v>4.601784944534302</v>
+        <v>4.287585020065308</v>
       </c>
       <c r="J40" t="n">
-        <v>4.344929456710815</v>
+        <v>4.320502758026123</v>
       </c>
       <c r="K40" t="n">
-        <v>4.400781869888306</v>
+        <v>4.046701431274414</v>
       </c>
       <c r="L40" t="n">
-        <v>4.468713641166687</v>
+        <v>4.221206450462342</v>
       </c>
     </row>
     <row r="41">
@@ -3944,37 +3944,37 @@
         <v>45</v>
       </c>
       <c r="B41" t="n">
-        <v>4.688563585281372</v>
+        <v>4.191814422607422</v>
       </c>
       <c r="C41" t="n">
-        <v>4.276087284088135</v>
+        <v>4.80585241317749</v>
       </c>
       <c r="D41" t="n">
-        <v>4.716487169265747</v>
+        <v>4.320510149002075</v>
       </c>
       <c r="E41" t="n">
-        <v>4.263633012771606</v>
+        <v>4.252667903900146</v>
       </c>
       <c r="F41" t="n">
-        <v>4.049670219421387</v>
+        <v>4.208285331726074</v>
       </c>
       <c r="G41" t="n">
-        <v>4.537927865982056</v>
+        <v>4.180366516113281</v>
       </c>
       <c r="H41" t="n">
-        <v>4.252668857574463</v>
+        <v>4.175855875015259</v>
       </c>
       <c r="I41" t="n">
-        <v>4.338426351547241</v>
+        <v>4.126031160354614</v>
       </c>
       <c r="J41" t="n">
-        <v>4.288604736328125</v>
+        <v>4.517014503479004</v>
       </c>
       <c r="K41" t="n">
-        <v>4.61724328994751</v>
+        <v>4.25266695022583</v>
       </c>
       <c r="L41" t="n">
-        <v>4.402931237220765</v>
+        <v>4.303106522560119</v>
       </c>
     </row>
     <row r="42">
@@ -3982,37 +3982,37 @@
         <v>46</v>
       </c>
       <c r="B42" t="n">
-        <v>4.22822117805481</v>
+        <v>4.365415096282959</v>
       </c>
       <c r="C42" t="n">
-        <v>4.364889621734619</v>
+        <v>4.334459066390991</v>
       </c>
       <c r="D42" t="n">
-        <v>4.259132385253906</v>
+        <v>4.188353061676025</v>
       </c>
       <c r="E42" t="n">
-        <v>4.136965274810791</v>
+        <v>4.549455642700195</v>
       </c>
       <c r="F42" t="n">
-        <v>4.2436842918396</v>
+        <v>4.234220504760742</v>
       </c>
       <c r="G42" t="n">
-        <v>4.187810897827148</v>
+        <v>4.40779185295105</v>
       </c>
       <c r="H42" t="n">
-        <v>4.070132970809937</v>
+        <v>4.333468437194824</v>
       </c>
       <c r="I42" t="n">
-        <v>4.406781435012817</v>
+        <v>4.331502676010132</v>
       </c>
       <c r="J42" t="n">
-        <v>4.315489053726196</v>
+        <v>4.581328868865967</v>
       </c>
       <c r="K42" t="n">
-        <v>4.730447769165039</v>
+        <v>4.098090887069702</v>
       </c>
       <c r="L42" t="n">
-        <v>4.294355487823486</v>
+        <v>4.342408609390259</v>
       </c>
     </row>
     <row r="43">
@@ -4020,37 +4020,37 @@
         <v>47</v>
       </c>
       <c r="B43" t="n">
-        <v>4.939446687698364</v>
+        <v>4.745399475097656</v>
       </c>
       <c r="C43" t="n">
-        <v>4.950876951217651</v>
+        <v>4.216265678405762</v>
       </c>
       <c r="D43" t="n">
-        <v>4.338437557220459</v>
+        <v>4.11202597618103</v>
       </c>
       <c r="E43" t="n">
-        <v>4.585350036621094</v>
+        <v>4.714510679244995</v>
       </c>
       <c r="F43" t="n">
-        <v>4.623211145401001</v>
+        <v>4.319018125534058</v>
       </c>
       <c r="G43" t="n">
-        <v>4.661636352539062</v>
+        <v>4.598782300949097</v>
       </c>
       <c r="H43" t="n">
-        <v>4.656111478805542</v>
+        <v>4.147480726242065</v>
       </c>
       <c r="I43" t="n">
-        <v>4.371873617172241</v>
+        <v>4.199308395385742</v>
       </c>
       <c r="J43" t="n">
-        <v>4.289560794830322</v>
+        <v>4.679100513458252</v>
       </c>
       <c r="K43" t="n">
-        <v>4.47258472442627</v>
+        <v>4.173387765884399</v>
       </c>
       <c r="L43" t="n">
-        <v>4.588908934593201</v>
+        <v>4.390527963638306</v>
       </c>
     </row>
     <row r="44">
@@ -4058,37 +4058,37 @@
         <v>48</v>
       </c>
       <c r="B44" t="n">
-        <v>4.393794298171997</v>
+        <v>3.968901395797729</v>
       </c>
       <c r="C44" t="n">
-        <v>4.161388158798218</v>
+        <v>4.107064485549927</v>
       </c>
       <c r="D44" t="n">
-        <v>3.967370271682739</v>
+        <v>4.134973287582397</v>
       </c>
       <c r="E44" t="n">
-        <v>4.11004900932312</v>
+        <v>4.086122274398804</v>
       </c>
       <c r="F44" t="n">
-        <v>4.738428115844727</v>
+        <v>4.114036560058594</v>
       </c>
       <c r="G44" t="n">
-        <v>4.288585662841797</v>
+        <v>4.078233480453491</v>
       </c>
       <c r="H44" t="n">
-        <v>4.257691383361816</v>
+        <v>3.938593864440918</v>
       </c>
       <c r="I44" t="n">
-        <v>4.114014625549316</v>
+        <v>4.181379318237305</v>
       </c>
       <c r="J44" t="n">
-        <v>4.159904479980469</v>
+        <v>4.098558902740479</v>
       </c>
       <c r="K44" t="n">
-        <v>4.216232776641846</v>
+        <v>3.973881721496582</v>
       </c>
       <c r="L44" t="n">
-        <v>4.240745878219604</v>
+        <v>4.068174529075622</v>
       </c>
     </row>
     <row r="45">
@@ -4096,37 +4096,37 @@
         <v>49</v>
       </c>
       <c r="B45" t="n">
-        <v>4.025733470916748</v>
+        <v>4.118023157119751</v>
       </c>
       <c r="C45" t="n">
-        <v>4.057177543640137</v>
+        <v>3.876656770706177</v>
       </c>
       <c r="D45" t="n">
-        <v>3.98084545135498</v>
+        <v>4.232397556304932</v>
       </c>
       <c r="E45" t="n">
-        <v>3.878088474273682</v>
+        <v>4.034755945205688</v>
       </c>
       <c r="F45" t="n">
-        <v>3.866639614105225</v>
+        <v>3.974895000457764</v>
       </c>
       <c r="G45" t="n">
-        <v>3.855161905288696</v>
+        <v>4.603306770324707</v>
       </c>
       <c r="H45" t="n">
-        <v>4.401774883270264</v>
+        <v>4.337466239929199</v>
       </c>
       <c r="I45" t="n">
-        <v>4.139449119567871</v>
+        <v>4.426735877990723</v>
       </c>
       <c r="J45" t="n">
-        <v>3.75590991973877</v>
+        <v>4.51003098487854</v>
       </c>
       <c r="K45" t="n">
-        <v>3.951410055160522</v>
+        <v>4.35393762588501</v>
       </c>
       <c r="L45" t="n">
-        <v>3.991219043731689</v>
+        <v>4.246820592880249</v>
       </c>
     </row>
     <row r="46">
@@ -4134,37 +4134,37 @@
         <v>5</v>
       </c>
       <c r="B46" t="n">
-        <v>4.0845627784729</v>
+        <v>4.303560972213745</v>
       </c>
       <c r="C46" t="n">
-        <v>4.210287809371948</v>
+        <v>4.229245185852051</v>
       </c>
       <c r="D46" t="n">
-        <v>4.309510231018066</v>
+        <v>4.499058961868286</v>
       </c>
       <c r="E46" t="n">
-        <v>3.967877864837646</v>
+        <v>3.946187734603882</v>
       </c>
       <c r="F46" t="n">
-        <v>4.184341907501221</v>
+        <v>4.001820087432861</v>
       </c>
       <c r="G46" t="n">
-        <v>4.20430064201355</v>
+        <v>3.986848831176758</v>
       </c>
       <c r="H46" t="n">
-        <v>4.025721073150635</v>
+        <v>3.961971759796143</v>
       </c>
       <c r="I46" t="n">
-        <v>4.070613145828247</v>
+        <v>4.653162002563477</v>
       </c>
       <c r="J46" t="n">
-        <v>4.100058078765869</v>
+        <v>4.254668951034546</v>
       </c>
       <c r="K46" t="n">
-        <v>4.146423578262329</v>
+        <v>3.981345415115356</v>
       </c>
       <c r="L46" t="n">
-        <v>4.130369710922241</v>
+        <v>4.18178699016571</v>
       </c>
     </row>
     <row r="47">
@@ -4172,37 +4172,37 @@
         <v>50</v>
       </c>
       <c r="B47" t="n">
-        <v>4.175854444503784</v>
+        <v>4.56437873840332</v>
       </c>
       <c r="C47" t="n">
-        <v>4.029226064682007</v>
+        <v>4.021754503250122</v>
       </c>
       <c r="D47" t="n">
-        <v>4.192800283432007</v>
+        <v>4.266637325286865</v>
       </c>
       <c r="E47" t="n">
-        <v>4.181336402893066</v>
+        <v>4.38335919380188</v>
       </c>
       <c r="F47" t="n">
-        <v>3.994842052459717</v>
+        <v>4.114023923873901</v>
       </c>
       <c r="G47" t="n">
-        <v>4.306526660919189</v>
+        <v>4.539486646652222</v>
       </c>
       <c r="H47" t="n">
-        <v>4.811743259429932</v>
+        <v>4.009796142578125</v>
       </c>
       <c r="I47" t="n">
-        <v>4.139953374862671</v>
+        <v>4.39580774307251</v>
       </c>
       <c r="J47" t="n">
-        <v>4.920953750610352</v>
+        <v>4.869580984115601</v>
       </c>
       <c r="K47" t="n">
-        <v>4.27160382270813</v>
+        <v>4.494057416915894</v>
       </c>
       <c r="L47" t="n">
-        <v>4.302484011650085</v>
+        <v>4.365888261795044</v>
       </c>
     </row>
     <row r="48">
@@ -4210,37 +4210,37 @@
         <v>6</v>
       </c>
       <c r="B48" t="n">
-        <v>4.437662601470947</v>
+        <v>4.240744113922119</v>
       </c>
       <c r="C48" t="n">
-        <v>4.319477796554565</v>
+        <v>4.800286293029785</v>
       </c>
       <c r="D48" t="n">
-        <v>4.907980918884277</v>
+        <v>4.243706941604614</v>
       </c>
       <c r="E48" t="n">
-        <v>4.458166837692261</v>
+        <v>4.486087799072266</v>
       </c>
       <c r="F48" t="n">
-        <v>4.179849147796631</v>
+        <v>4.212286472320557</v>
       </c>
       <c r="G48" t="n">
-        <v>4.614242792129517</v>
+        <v>4.597782850265503</v>
       </c>
       <c r="H48" t="n">
-        <v>4.319982290267944</v>
+        <v>4.482088088989258</v>
       </c>
       <c r="I48" t="n">
-        <v>4.092581510543823</v>
+        <v>4.732460975646973</v>
       </c>
       <c r="J48" t="n">
-        <v>4.154417991638184</v>
+        <v>4.31551456451416</v>
       </c>
       <c r="K48" t="n">
-        <v>4.265133380889893</v>
+        <v>4.406850576400757</v>
       </c>
       <c r="L48" t="n">
-        <v>4.374949526786804</v>
+        <v>4.451780867576599</v>
       </c>
     </row>
     <row r="49">
@@ -4248,37 +4248,37 @@
         <v>7</v>
       </c>
       <c r="B49" t="n">
-        <v>4.784824848175049</v>
+        <v>4.664641141891479</v>
       </c>
       <c r="C49" t="n">
-        <v>4.793367385864258</v>
+        <v>4.434715747833252</v>
       </c>
       <c r="D49" t="n">
-        <v>4.467033863067627</v>
+        <v>4.67461371421814</v>
       </c>
       <c r="E49" t="n">
-        <v>4.801932334899902</v>
+        <v>4.568890571594238</v>
       </c>
       <c r="F49" t="n">
-        <v>4.810737609863281</v>
+        <v>4.906108617782593</v>
       </c>
       <c r="G49" t="n">
-        <v>4.615329027175903</v>
+        <v>4.731334686279297</v>
       </c>
       <c r="H49" t="n">
-        <v>4.217275857925415</v>
+        <v>4.692801237106323</v>
       </c>
       <c r="I49" t="n">
-        <v>4.155405521392822</v>
+        <v>4.371625423431396</v>
       </c>
       <c r="J49" t="n">
-        <v>4.681055307388306</v>
+        <v>4.839432239532471</v>
       </c>
       <c r="K49" t="n">
-        <v>4.768853187561035</v>
+        <v>4.324753761291504</v>
       </c>
       <c r="L49" t="n">
-        <v>4.60958149433136</v>
+        <v>4.62089171409607</v>
       </c>
     </row>
     <row r="50">
@@ -4286,37 +4286,37 @@
         <v>8</v>
       </c>
       <c r="B50" t="n">
-        <v>3.757441520690918</v>
+        <v>3.812123537063599</v>
       </c>
       <c r="C50" t="n">
-        <v>3.506557464599609</v>
+        <v>3.465989589691162</v>
       </c>
       <c r="D50" t="n">
-        <v>3.505557298660278</v>
+        <v>3.731915473937988</v>
       </c>
       <c r="E50" t="n">
-        <v>4.203307390213013</v>
+        <v>3.51094913482666</v>
       </c>
       <c r="F50" t="n">
-        <v>3.614790201187134</v>
+        <v>3.450015306472778</v>
       </c>
       <c r="G50" t="n">
-        <v>3.701559066772461</v>
+        <v>3.728807210922241</v>
       </c>
       <c r="H50" t="n">
-        <v>3.752452611923218</v>
+        <v>3.68192982673645</v>
       </c>
       <c r="I50" t="n">
-        <v>3.450210571289062</v>
+        <v>3.49341607093811</v>
       </c>
       <c r="J50" t="n">
-        <v>3.485619068145752</v>
+        <v>3.54926872253418</v>
       </c>
       <c r="K50" t="n">
-        <v>3.623756170272827</v>
+        <v>3.890436410903931</v>
       </c>
       <c r="L50" t="n">
-        <v>3.660125136375427</v>
+        <v>3.63148512840271</v>
       </c>
     </row>
     <row r="51">
@@ -4324,37 +4324,37 @@
         <v>9</v>
       </c>
       <c r="B51" t="n">
-        <v>4.049183130264282</v>
+        <v>4.204081773757935</v>
       </c>
       <c r="C51" t="n">
-        <v>4.448646306991577</v>
+        <v>4.389588117599487</v>
       </c>
       <c r="D51" t="n">
-        <v>4.387815237045288</v>
+        <v>4.223035573959351</v>
       </c>
       <c r="E51" t="n">
-        <v>4.201281547546387</v>
+        <v>4.18515682220459</v>
       </c>
       <c r="F51" t="n">
-        <v>4.112010955810547</v>
+        <v>4.09883975982666</v>
       </c>
       <c r="G51" t="n">
-        <v>4.11899209022522</v>
+        <v>4.118800401687622</v>
       </c>
       <c r="H51" t="n">
-        <v>4.241209745407104</v>
+        <v>3.879897117614746</v>
       </c>
       <c r="I51" t="n">
-        <v>4.18333101272583</v>
+        <v>4.15922212600708</v>
       </c>
       <c r="J51" t="n">
-        <v>4.298565149307251</v>
+        <v>4.267410278320312</v>
       </c>
       <c r="K51" t="n">
-        <v>4.167853593826294</v>
+        <v>4.267906188964844</v>
       </c>
       <c r="L51" t="n">
-        <v>4.220888876914978</v>
+        <v>4.179393815994263</v>
       </c>
     </row>
     <row r="52">
@@ -4364,37 +4364,37 @@
         </is>
       </c>
       <c r="B52" t="n">
-        <v>4.266401543617248</v>
+        <v>4.23902575969696</v>
       </c>
       <c r="C52" t="n">
-        <v>4.282431344985962</v>
+        <v>4.263061509132386</v>
       </c>
       <c r="D52" t="n">
-        <v>4.268812489509583</v>
+        <v>4.196948866844178</v>
       </c>
       <c r="E52" t="n">
-        <v>4.261319322586059</v>
+        <v>4.236909461021424</v>
       </c>
       <c r="F52" t="n">
-        <v>4.284824995994568</v>
+        <v>4.173118300437928</v>
       </c>
       <c r="G52" t="n">
-        <v>4.261087694168091</v>
+        <v>4.23055109500885</v>
       </c>
       <c r="H52" t="n">
-        <v>4.304109044075012</v>
+        <v>4.200947275161743</v>
       </c>
       <c r="I52" t="n">
-        <v>4.243944077491761</v>
+        <v>4.256403589248658</v>
       </c>
       <c r="J52" t="n">
-        <v>4.245328960418701</v>
+        <v>4.279062690734864</v>
       </c>
       <c r="K52" t="n">
-        <v>4.286263122558593</v>
+        <v>4.168239030838013</v>
       </c>
       <c r="L52" t="n">
-        <v>4.270452259540559</v>
+        <v>4.2244267578125</v>
       </c>
     </row>
   </sheetData>
